--- a/gym/GymLogbuch_Beine.xlsx
+++ b/gym/GymLogbuch_Beine.xlsx
@@ -31,9 +31,9 @@
     <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Titles" vbProcedure="false">Progression!$1:$3</definedName>
     <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">Rekorde!$A$1:$N$19</definedName>
     <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Titles" vbProcedure="false">Rekorde!$1:$3</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Start!$B$1:$E$38</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Start!$B$1:$E$41</definedName>
     <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">Trainingsblatt!$A$1:$H$98</definedName>
-    <definedName function="false" hidden="false" localSheetId="8" name="_xlnm.Print_Area" vbProcedure="false">Übungen!$A$1:$F$19</definedName>
+    <definedName function="false" hidden="false" localSheetId="8" name="_xlnm.Print_Area" vbProcedure="false">Übungen!$A$1:$J$19</definedName>
     <definedName function="false" hidden="false" localSheetId="8" name="_xlnm.Print_Titles" vbProcedure="false">Übungen!$1:$3</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="212">
   <si>
     <t xml:space="preserve">GYM LOGBUCH  |  BEINTRAINING</t>
   </si>
@@ -139,7 +139,7 @@
     <t xml:space="preserve">Blatt 'Übungen'</t>
   </si>
   <si>
-    <t xml:space="preserve">Stammdaten. Hier neue Übungen ergänzen - sie erscheinen automatisch in den Dropdowns und in allen Auswertungen.</t>
+    <t xml:space="preserve">Stammdaten und Planvorgaben: Ziel-Wdh, Ziel-Sätze, Ziel-RPE und Startgewicht je Übung. Neue Übung hier ergänzen - sie erscheint automatisch in den Dropdowns und in allen Auswertungen. 'Aktiv = nein' archiviert eine Übung: raus aus der Planung, Historie bleibt.</t>
   </si>
   <si>
     <t xml:space="preserve">Legende</t>
@@ -190,7 +190,13 @@
     <t xml:space="preserve">RPE</t>
   </si>
   <si>
-    <t xml:space="preserve">Anstrengung 6 bis 10. 10 = keine Wiederholung mehr möglich. Optional, aber sehr hilfreich für die Steuerung.</t>
+    <t xml:space="preserve">Anstrengung 6 bis 10. 10 = keine Wiederholung mehr möglich. Optional, aber sehr hilfreich für die Steuerung. Die Zielwerte je Übung stehen im Blatt 'Übungen'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Archiv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Übung im Blatt 'Übungen' auf Aktiv = nein setzen. Sie verschwindet aus dem Trainingsblatt, bleibt in Log, Auswertung, Progression und Rekorden aber sichtbar - dort grau und kursiv.</t>
   </si>
   <si>
     <t xml:space="preserve">Offene Punkte aus der Originalquelle</t>
@@ -223,13 +229,25 @@
     <t xml:space="preserve">Lunges</t>
   </si>
   <si>
-    <t xml:space="preserve">Nur Gewichte, keine Wdh und keine Satzstruktur. Als je ein Arbeitssatz in Einheit 1 bis 3 erfasst - deshalb bleibt das Volumen dort leer.</t>
+    <t xml:space="preserve">Nur Gewichte, keine Wdh und keine Satzstruktur. Als je ein Arbeitssatz in Einheit 1 bis 3 erfasst - deshalb bleibt das Volumen dort leer. Übung ist inzwischen archiviert.</t>
   </si>
   <si>
     <t xml:space="preserve">Datum</t>
   </si>
   <si>
     <t xml:space="preserve">In der Quelle nicht enthalten. Im Blatt 'Einheiten' nachtragen, falls du die Termine noch weisst.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stackende Adduktion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.5 kg ist das Ende des Steckgewichts. Im Blatt 'Übungen' als 'Max (kg)' hinterlegt, damit der Zielvorschlag dort stehen bleibt statt eine Last zu fordern, die die Maschine nicht hergibt. Weitersteigern über Tempo und Pausen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Startgewichte fehlen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hackenschmidt-Kniebeuge und Rumänisches Kreuzheben sind neu im Plan und haben keine Historie. Trag im Blatt 'Übungen' unter 'Start (kg)' ein Einstiegsgewicht ein, dann füllt sich die Plan-Spalte des Trainingsblatts. Aus den bisherigen Daten lässt sich dafür kein seriöser Wert ableiten - das entscheidest du im ersten Satz.</t>
   </si>
   <si>
     <t xml:space="preserve">Alle Kennzahlen sind Formeln. Sobald du im Log Zeilen ergänzt, aktualisieren sich Auswertung, Progression, Rekorde und Dashboard von selbst.</t>
@@ -541,7 +559,7 @@
 Ziel (kg)</t>
   </si>
   <si>
-    <t xml:space="preserve">Nächstes Ziel = letztes Top-Gewicht plus 2.5 Prozent, gerundet auf 0.5 kg. Richtwert, keine Vorgabe - an Maschinen bestimmt die Steckplatte den Sprung.</t>
+    <t xml:space="preserve">Nächstes Ziel = letztes Top-Gewicht plus 2.5 Prozent, gerundet auf 0.5 kg, begrenzt durch 'Max (kg)' aus dem Blatt 'Übungen'. Ohne Historie greift stattdessen das Startgewicht. Richtwert, keine Vorgabe - an Maschinen bestimmt die Steckplatte den Sprung.   ·   Graue, kursive Zeilen sind archivierte Übungen: nicht mehr im Plan, Historie bleibt.</t>
   </si>
   <si>
     <t xml:space="preserve">TRAININGSBLATT  |  BEINE VORNE</t>
@@ -580,10 +598,10 @@
     <t xml:space="preserve">TRAININGSBLATT  |  BEINE HINTEN</t>
   </si>
   <si>
-    <t xml:space="preserve">ÜBUNGEN  |  STAMMDATEN</t>
+    <t xml:space="preserve">ÜBUNGEN  |  STAMMDATEN UND PLANVORGABEN</t>
   </si>
   <si>
-    <t xml:space="preserve">Neue Übung hier ergänzen - Dropdowns und Auswertungen ziehen automatisch nach.</t>
+    <t xml:space="preserve">Neue Übung hier ergänzen - Dropdowns, Trainingsblatt und Auswertungen ziehen automatisch nach. Aktiv = nein heisst Archiv: die Übung verschwindet aus der Planung, ihre Historie bleibt in Log und Auswertung erhalten.</t>
   </si>
   <si>
     <t xml:space="preserve">Gerät / Variante</t>
@@ -592,58 +610,129 @@
     <t xml:space="preserve">Ziel-Wdh</t>
   </si>
   <si>
+    <t xml:space="preserve">Ziel-
+Sätze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ziel-
+RPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max (kg)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Aktiv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hackenschmidt-Kniebeuge</t>
   </si>
   <si>
     <t xml:space="preserve">Beine vorne</t>
   </si>
   <si>
+    <t xml:space="preserve">Hackenschmidt / Pendel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8-9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ersetzt Lunges. Schwere Grundübung zuerst, Quadrizeps unter Last in der gedehnten Position, Rücken gestützt. Ohne Maschine: Pendelkniebeuge, sonst Beinpresse mit tiefer Fussposition.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multipresse / Hantel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wdh-Bereich von 5-8 auf 8-10 je Bein. Limiter soll der Muskel sein, nicht die Stabilität.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Maschine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dritter Arbeitssatz läuft als Reduktionssatz aus.</t>
   </si>
   <si>
     <t xml:space="preserve">15-20</t>
   </si>
   <si>
-    <t xml:space="preserve">ja</t>
+    <t xml:space="preserve">152.5 kg ist Stackende. Progression ab jetzt über 3 s Exzentrik und 1 s Pause in der gedehnten Position, nicht über Last.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rumänisches Kreuzheben</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beine hinten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langhantel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ersetzt Kickback. Schliesst die Lücke Hüftstreckung bei gestrecktem Knie, Ischiokrurale und Gluteus in der Dehnung.</t>
   </si>
   <si>
     <t xml:space="preserve">8-12</t>
   </si>
   <si>
-    <t xml:space="preserve">Multipresse / Hantel</t>
+    <t xml:space="preserve">Gesamtgewicht inkl. Stange notieren, auch bei Reduktionssätzen.</t>
   </si>
   <si>
-    <t xml:space="preserve">5-8</t>
+    <t xml:space="preserve">Maschine, sitzend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sitzend statt liegend: Hüfte gebeugt, Ischiokrurale vorgedehnt, mehr Reiz pro Satz. Dritter Satz als Reduktionssatz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kabel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gluteus medius, relevant für die Silhouette von vorne.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In jede Beineinheit, bisher nur in jeder zweiten.</t>
   </si>
   <si>
     <t xml:space="preserve">Kurzhantel</t>
   </si>
   <si>
-    <t xml:space="preserve">10-12</t>
+    <t xml:space="preserve">nein</t>
   </si>
   <si>
-    <t xml:space="preserve">Beine hinten</t>
+    <t xml:space="preserve">Archiv. Redundant zum Split Squat, Historie bleibt in den Auswertungen sichtbar.</t>
   </si>
   <si>
     <t xml:space="preserve">Maschine / Kabel</t>
   </si>
   <si>
-    <t xml:space="preserve">10-15</t>
+    <t xml:space="preserve">Archiv. Von Hip Thrust und RDL abgedeckt, Historie bleibt erhalten.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kabel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Langhantel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Die Reihenfolge hier ist die Reihenfolge in allen Auswertungen und auf dem Trainingsblatt.</t>
+    <t xml:space="preserve">Reihenfolge hier = Reihenfolge in allen Auswertungen und auf dem Trainingsblatt.   ·   'Start (kg)' braucht nur eine Übung ohne Historie: solange keine Arbeitssätze im Log stehen, speist dieser Wert die Plan-Spalte des Trainingsblatts. Sobald die erste Einheit erfasst ist, rechnet das Logbuch aus den echten Werten weiter.   ·   'Max (kg)' begrenzt den Zielvorschlag nach oben, etwa am Ende des Steckgewichts - darüber steigerst du über Tempo, Pausen und Wiederholungen statt über Last.   ·   Archivierte Übungen erscheinen grau und tauchen im Trainingsblatt nicht mehr auf.</t>
   </si>
 </sst>
 </file>
@@ -657,7 +746,7 @@
     <numFmt numFmtId="167" formatCode="dd\.mm\.yyyy"/>
     <numFmt numFmtId="168" formatCode="\+0.0%;\-0.0%;\–"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -802,6 +891,14 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FF8A94A0"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -935,7 +1032,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="64">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1172,6 +1269,26 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1181,7 +1298,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="12">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1256,6 +1373,16 @@
         <name val="Arial"/>
         <charset val="1"/>
         <family val="0"/>
+        <i val="1"/>
+        <color rgb="FF8A94A0"/>
+        <sz val="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
         <b val="1"/>
         <color rgb="FF15803D"/>
         <sz val="10"/>
@@ -1321,7 +1448,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF3D6288"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF8A94A0"/>
       <rgbColor rgb="FF142A44"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -1536,11 +1663,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="64588510"/>
-        <c:axId val="26015228"/>
+        <c:axId val="8640544"/>
+        <c:axId val="5861995"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="64588510"/>
+        <c:axId val="8640544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1606,7 +1733,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26015228"/>
+        <c:crossAx val="5861995"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1614,7 +1741,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="26015228"/>
+        <c:axId val="5861995"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -1657,7 +1784,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64588510"/>
+        <c:crossAx val="8640544"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1784,48 +1911,51 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Rekorde!$A$4:$A$12</c:f>
+              <c:f>Rekorde!$A$4:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
+                  <c:v>Hackenschmidt-Kniebeuge</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Split Squat</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Beinstrecker</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>Adduktion</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>Beinstrecker</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Split Squat</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Lunges</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>Kickback</c:v>
+                  <c:v>Rumänisches Kreuzheben</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Seitliche Kickbacks</c:v>
+                  <c:v>Hip Thrust</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Beinbeuger</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Hip Thrust</c:v>
+                  <c:v>Seitliche Kickbacks</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>Waden</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Lunges</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Kickback</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Rekorde!$L$4:$L$12</c:f>
+              <c:f>Rekorde!$L$4:$L$14</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.0;\-#,##0.0;\–</c:formatCode>
-                <c:ptCount val="9"/>
-                <c:pt idx="0">
-                  <c:v>152.5</c:v>
-                </c:pt>
+                <c:ptCount val="11"/>
                 <c:pt idx="1">
                   <c:v>80</c:v>
                 </c:pt>
@@ -1833,22 +1963,25 @@
                   <c:v>80</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>63</c:v>
+                  <c:v>152.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>35</c:v>
+                  <c:v>270</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>270</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>63</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1908,71 +2041,77 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Rekorde!$A$4:$A$12</c:f>
+              <c:f>Rekorde!$A$4:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
+                  <c:v>Hackenschmidt-Kniebeuge</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Split Squat</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Beinstrecker</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>Adduktion</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>Beinstrecker</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Split Squat</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Lunges</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>Kickback</c:v>
+                  <c:v>Rumänisches Kreuzheben</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Seitliche Kickbacks</c:v>
+                  <c:v>Hip Thrust</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Beinbeuger</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Hip Thrust</c:v>
+                  <c:v>Seitliche Kickbacks</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>Waden</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Lunges</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Kickback</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Rekorde!$F$4:$F$12</c:f>
+              <c:f>Rekorde!$F$4:$F$14</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.0;\-#,##0.0;\–</c:formatCode>
-                <c:ptCount val="9"/>
-                <c:pt idx="0">
+                <c:ptCount val="11"/>
+                <c:pt idx="1">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>152.5</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>85</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>105</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>84</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>49</c:v>
+                  <c:v>280</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>55</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>280</c:v>
+                  <c:v>49</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>84</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1980,11 +2119,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="74910867"/>
-        <c:axId val="77389406"/>
+        <c:axId val="49251609"/>
+        <c:axId val="53763068"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="74910867"/>
+        <c:axId val="49251609"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2016,7 +2155,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77389406"/>
+        <c:crossAx val="53763068"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2024,7 +2163,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="77389406"/>
+        <c:axId val="53763068"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2067,7 +2206,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74910867"/>
+        <c:crossAx val="49251609"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2218,71 +2357,77 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Rekorde!$A$4:$A$12</c:f>
+              <c:f>Rekorde!$A$4:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
+                  <c:v>Hackenschmidt-Kniebeuge</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Split Squat</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Beinstrecker</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>Adduktion</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>Beinstrecker</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Split Squat</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Lunges</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>Kickback</c:v>
+                  <c:v>Rumänisches Kreuzheben</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Seitliche Kickbacks</c:v>
+                  <c:v>Hip Thrust</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Beinbeuger</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Hip Thrust</c:v>
+                  <c:v>Seitliche Kickbacks</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>Waden</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Lunges</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Kickback</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Rekorde!$E$4:$E$12</c:f>
+              <c:f>Rekorde!$E$4:$E$14</c:f>
               <c:numCache>
                 <c:formatCode>#,##0;\-#,##0;\–</c:formatCode>
-                <c:ptCount val="9"/>
-                <c:pt idx="0">
+                <c:ptCount val="11"/>
+                <c:pt idx="1">
+                  <c:v>7100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5865</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>21807.5</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>5865</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>7100</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>7119</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>2053</c:v>
+                  <c:v>20060</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>3555</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>20060</c:v>
+                  <c:v>2053</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>6945</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2290,11 +2435,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="22357093"/>
-        <c:axId val="9095830"/>
+        <c:axId val="34101083"/>
+        <c:axId val="70106502"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="22357093"/>
+        <c:axId val="34101083"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2326,7 +2471,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9095830"/>
+        <c:crossAx val="70106502"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2334,7 +2479,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="9095830"/>
+        <c:axId val="70106502"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2377,7 +2522,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22357093"/>
+        <c:crossAx val="34101083"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2504,68 +2649,74 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Rekorde!$A$4:$A$12</c:f>
+              <c:f>Rekorde!$A$4:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
+                  <c:v>Hackenschmidt-Kniebeuge</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Split Squat</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Beinstrecker</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>Adduktion</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>Beinstrecker</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Split Squat</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Lunges</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>Kickback</c:v>
+                  <c:v>Rumänisches Kreuzheben</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Seitliche Kickbacks</c:v>
+                  <c:v>Hip Thrust</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Beinbeuger</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Hip Thrust</c:v>
+                  <c:v>Seitliche Kickbacks</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>Waden</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Lunges</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Kickback</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Rekorde!$H$4:$H$12</c:f>
+              <c:f>Rekorde!$H$4:$H$14</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.0;\-#,##0.0;\–</c:formatCode>
-                <c:ptCount val="9"/>
-                <c:pt idx="0">
+                <c:ptCount val="11"/>
+                <c:pt idx="1">
+                  <c:v>123.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>279.583333333333</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>112</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>123.5</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>117.6</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>68.6</c:v>
+                  <c:v>360</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>73.3333333333333</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>360</c:v>
+                  <c:v>68.6</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>117.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2573,11 +2724,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="946452"/>
-        <c:axId val="69318535"/>
+        <c:axId val="3429732"/>
+        <c:axId val="59816477"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="946452"/>
+        <c:axId val="3429732"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2609,7 +2760,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69318535"/>
+        <c:crossAx val="59816477"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2617,7 +2768,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="69318535"/>
+        <c:axId val="59816477"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2660,7 +2811,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="946452"/>
+        <c:crossAx val="3429732"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2997,7 +3148,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:E38"/>
+  <dimension ref="B1:E41"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -3103,7 +3254,7 @@
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
     </row>
-    <row r="13" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="7" t="s">
         <v>12</v>
       </c>
@@ -3113,7 +3264,7 @@
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
     </row>
-    <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="7" t="s">
         <v>14</v>
       </c>
@@ -3123,7 +3274,7 @@
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
     </row>
-    <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="s">
         <v>16</v>
       </c>
@@ -3133,7 +3284,7 @@
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
     </row>
-    <row r="16" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="7" t="s">
         <v>18</v>
       </c>
@@ -3143,7 +3294,7 @@
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
     </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="7" t="s">
         <v>20</v>
       </c>
@@ -3153,7 +3304,7 @@
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
     </row>
-    <row r="18" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="7" t="s">
         <v>22</v>
       </c>
@@ -3171,7 +3322,7 @@
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="9" t="s">
         <v>25</v>
       </c>
@@ -3181,7 +3332,7 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
     </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="7" t="s">
         <v>27</v>
       </c>
@@ -3191,7 +3342,7 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
     </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="7" t="s">
         <v>29</v>
       </c>
@@ -3201,7 +3352,7 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
     </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="7" t="s">
         <v>31</v>
       </c>
@@ -3221,7 +3372,7 @@
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
     </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="7" t="s">
         <v>35</v>
       </c>
@@ -3241,7 +3392,7 @@
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
     </row>
-    <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="7" t="s">
         <v>39</v>
       </c>
@@ -3251,25 +3402,25 @@
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
     </row>
-    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="3" t="s">
+    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-    </row>
-    <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="10" t="s">
+      <c r="C29" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+    </row>
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-    </row>
-    <row r="32" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+    </row>
+    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="10" t="s">
         <v>44</v>
       </c>
@@ -3279,7 +3430,7 @@
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
     </row>
-    <row r="33" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="10" t="s">
         <v>46</v>
       </c>
@@ -3289,7 +3440,7 @@
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
     </row>
-    <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="10" t="s">
         <v>48</v>
       </c>
@@ -3299,7 +3450,7 @@
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
     </row>
-    <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="10" t="s">
         <v>50</v>
       </c>
@@ -3309,7 +3460,7 @@
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
     </row>
-    <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="10" t="s">
         <v>52</v>
       </c>
@@ -3319,16 +3470,46 @@
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="11" t="s">
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
+      <c r="C37" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+    </row>
+    <row r="38" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+    </row>
+    <row r="39" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="36">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="B4:E4"/>
@@ -3354,14 +3535,17 @@
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="C28:E28"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="B31:E31"/>
     <mergeCell ref="C32:E32"/>
     <mergeCell ref="C33:E33"/>
     <mergeCell ref="C34:E34"/>
     <mergeCell ref="C35:E35"/>
     <mergeCell ref="C36:E36"/>
-    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="B41:E41"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.5" right="0.4" top="0.7" bottom="0.6" header="0.3" footer="0.3"/>
@@ -3395,7 +3579,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3409,7 +3593,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3423,7 +3607,7 @@
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="12" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C4" s="12"/>
       <c r="E4" s="12" t="s">
@@ -3431,7 +3615,7 @@
       </c>
       <c r="F4" s="12"/>
       <c r="H4" s="12" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="I4" s="12"/>
     </row>
@@ -3458,11 +3642,11 @@
       </c>
       <c r="C7" s="12"/>
       <c r="E7" s="12" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F7" s="12"/>
       <c r="H7" s="12" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="I7" s="12"/>
     </row>
@@ -3485,15 +3669,15 @@
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="12" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C10" s="12"/>
       <c r="E10" s="12" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F10" s="12"/>
       <c r="H10" s="12" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="I10" s="12"/>
     </row>
@@ -3510,13 +3694,13 @@
       <c r="F11" s="14"/>
       <c r="H11" s="13" t="n">
         <f aca="false">COUNTA(Übungen!$A$4:$A$17)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I11" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -3529,7 +3713,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="15" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -3588,7 +3772,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3603,7 +3787,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3618,37 +3802,37 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="J3" s="16" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K3" s="16" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4229,7 +4413,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="23" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B28" s="24"/>
       <c r="C28" s="24"/>
@@ -4253,7 +4437,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -4261,6 +4445,12 @@
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C4:C27" type="list">
+      <formula1>"Beine vorne,Beine hinten,Beine komplett"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.5" right="0.4" top="0.7" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4294,7 +4484,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4310,7 +4500,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4326,40 +4516,40 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H3" s="16" t="s">
         <v>39</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="J3" s="16" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K3" s="16" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="L3" s="16" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4375,10 +4565,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F4" s="20" t="n">
         <v>77.5</v>
@@ -4411,10 +4601,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F5" s="20" t="n">
         <v>152.5</v>
@@ -4447,10 +4637,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F6" s="20" t="n">
         <v>152.5</v>
@@ -4483,10 +4673,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F7" s="20" t="n">
         <v>110</v>
@@ -4504,7 +4694,7 @@
         <v/>
       </c>
       <c r="K7" s="19" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="L7" s="19"/>
     </row>
@@ -4521,10 +4711,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F8" s="20" t="n">
         <v>85</v>
@@ -4557,10 +4747,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F9" s="20" t="n">
         <v>152.5</v>
@@ -4593,10 +4783,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F10" s="20" t="n">
         <v>152.5</v>
@@ -4629,10 +4819,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F11" s="20" t="n">
         <v>110</v>
@@ -4650,7 +4840,7 @@
         <v/>
       </c>
       <c r="K11" s="19" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="L11" s="19"/>
     </row>
@@ -4667,10 +4857,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F12" s="20" t="n">
         <v>65</v>
@@ -4703,10 +4893,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F13" s="20" t="n">
         <v>80</v>
@@ -4739,10 +4929,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F14" s="20" t="n">
         <v>152.5</v>
@@ -4775,10 +4965,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F15" s="20" t="n">
         <v>152.5</v>
@@ -4811,10 +5001,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F16" s="20" t="n">
         <v>110</v>
@@ -4832,7 +5022,7 @@
         <v/>
       </c>
       <c r="K16" s="19" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="L16" s="19"/>
     </row>
@@ -4849,10 +5039,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F17" s="20" t="n">
         <v>50</v>
@@ -4885,10 +5075,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F18" s="20" t="n">
         <v>70</v>
@@ -4921,10 +5111,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F19" s="20" t="n">
         <v>152.5</v>
@@ -4943,7 +5133,7 @@
       </c>
       <c r="K19" s="19"/>
       <c r="L19" s="19" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4959,10 +5149,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F20" s="20" t="n">
         <v>152.5</v>
@@ -4981,7 +5171,7 @@
       </c>
       <c r="K20" s="19"/>
       <c r="L20" s="19" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4997,10 +5187,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F21" s="20" t="n">
         <v>125</v>
@@ -5018,7 +5208,7 @@
         <v/>
       </c>
       <c r="K21" s="19" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="L21" s="19"/>
     </row>
@@ -5035,10 +5225,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F22" s="20" t="n">
         <v>15</v>
@@ -5071,10 +5261,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F23" s="20" t="n">
         <v>30</v>
@@ -5107,10 +5297,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F24" s="20" t="n">
         <v>65</v>
@@ -5143,10 +5333,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F25" s="20" t="n">
         <v>75</v>
@@ -5179,10 +5369,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D26" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="E26" s="17" t="s">
         <v>99</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>93</v>
       </c>
       <c r="F26" s="20" t="n">
         <v>55</v>
@@ -5198,10 +5388,10 @@
         <v/>
       </c>
       <c r="K26" s="19" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="L26" s="19" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5217,10 +5407,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F27" s="20" t="n">
         <v>10</v>
@@ -5237,7 +5427,7 @@
       </c>
       <c r="K27" s="19"/>
       <c r="L27" s="19" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5253,10 +5443,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F28" s="20" t="n">
         <v>20</v>
@@ -5273,7 +5463,7 @@
       </c>
       <c r="K28" s="19"/>
       <c r="L28" s="19" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5289,10 +5479,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F29" s="20" t="n">
         <v>70</v>
@@ -5325,10 +5515,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F30" s="20" t="n">
         <v>80</v>
@@ -5361,10 +5551,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D31" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="E31" s="17" t="s">
         <v>99</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>93</v>
       </c>
       <c r="F31" s="20" t="n">
         <v>60</v>
@@ -5382,7 +5572,7 @@
         <v/>
       </c>
       <c r="K31" s="19" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="L31" s="19"/>
     </row>
@@ -5399,10 +5589,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F32" s="20" t="n">
         <v>15</v>
@@ -5435,10 +5625,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F33" s="20" t="n">
         <v>25</v>
@@ -5471,10 +5661,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F34" s="20" t="n">
         <v>85</v>
@@ -5507,10 +5697,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F35" s="20" t="n">
         <v>75</v>
@@ -5543,10 +5733,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D36" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="E36" s="17" t="s">
         <v>99</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>93</v>
       </c>
       <c r="F36" s="20" t="n">
         <v>65</v>
@@ -5564,7 +5754,7 @@
         <v/>
       </c>
       <c r="K36" s="19" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="L36" s="19"/>
     </row>
@@ -5581,10 +5771,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F37" s="20" t="n">
         <v>15</v>
@@ -5617,10 +5807,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F38" s="20" t="n">
         <v>30</v>
@@ -5653,10 +5843,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D39" s="19" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F39" s="20" t="n">
         <v>80</v>
@@ -5689,10 +5879,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D40" s="19" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F40" s="20" t="n">
         <v>80</v>
@@ -5725,10 +5915,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D41" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="E41" s="17" t="s">
         <v>99</v>
-      </c>
-      <c r="E41" s="17" t="s">
-        <v>93</v>
       </c>
       <c r="F41" s="20" t="n">
         <v>70</v>
@@ -5746,7 +5936,7 @@
         <v/>
       </c>
       <c r="K41" s="19" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L41" s="19"/>
     </row>
@@ -5763,10 +5953,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F42" s="20" t="n">
         <v>20</v>
@@ -5799,10 +5989,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F43" s="20" t="n">
         <v>40</v>
@@ -5835,10 +6025,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E44" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F44" s="20" t="n">
         <v>80</v>
@@ -5871,10 +6061,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E45" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F45" s="20" t="n">
         <v>90</v>
@@ -5907,10 +6097,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F46" s="20" t="n">
         <v>100</v>
@@ -5943,10 +6133,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F47" s="20" t="n">
         <v>30</v>
@@ -5979,10 +6169,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D48" s="19" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F48" s="20" t="n">
         <v>50</v>
@@ -6015,10 +6205,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D49" s="19" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F49" s="20" t="n">
         <v>85</v>
@@ -6051,10 +6241,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F50" s="20" t="n">
         <v>95</v>
@@ -6087,10 +6277,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F51" s="20" t="n">
         <v>105</v>
@@ -6123,10 +6313,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D52" s="19" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F52" s="20" t="n">
         <v>40</v>
@@ -6159,10 +6349,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F53" s="20" t="n">
         <v>60</v>
@@ -6195,10 +6385,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D54" s="19" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F54" s="20" t="n">
         <v>100</v>
@@ -6231,10 +6421,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D55" s="19" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F55" s="20" t="n">
         <v>95</v>
@@ -6267,10 +6457,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D56" s="19" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F56" s="20" t="n">
         <v>90</v>
@@ -6303,10 +6493,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F57" s="20" t="n">
         <v>40</v>
@@ -6339,10 +6529,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E58" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F58" s="20" t="n">
         <v>70</v>
@@ -6375,10 +6565,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E59" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F59" s="20" t="n">
         <v>80</v>
@@ -6411,10 +6601,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E60" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F60" s="20" t="n">
         <v>60</v>
@@ -6447,10 +6637,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F61" s="20" t="n">
         <v>50</v>
@@ -6483,10 +6673,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E62" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F62" s="20" t="n">
         <v>10</v>
@@ -6503,7 +6693,7 @@
       </c>
       <c r="K62" s="19"/>
       <c r="L62" s="19" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6519,10 +6709,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E63" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F63" s="20" t="n">
         <v>16</v>
@@ -6539,7 +6729,7 @@
       </c>
       <c r="K63" s="19"/>
       <c r="L63" s="19" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6555,10 +6745,10 @@
         <v>Beine vorne</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E64" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F64" s="20" t="n">
         <v>18</v>
@@ -6575,7 +6765,7 @@
       </c>
       <c r="K64" s="19"/>
       <c r="L64" s="19" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6591,10 +6781,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E65" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F65" s="20" t="n">
         <v>35</v>
@@ -6611,7 +6801,7 @@
       </c>
       <c r="K65" s="19"/>
       <c r="L65" s="19" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6627,10 +6817,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D66" s="19" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E66" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F66" s="20" t="n">
         <v>49</v>
@@ -6647,7 +6837,7 @@
       </c>
       <c r="K66" s="19"/>
       <c r="L66" s="19" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6663,10 +6853,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E67" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F67" s="20" t="n">
         <v>70</v>
@@ -6699,10 +6889,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D68" s="19" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E68" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F68" s="20" t="n">
         <v>77</v>
@@ -6735,10 +6925,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E69" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F69" s="20" t="n">
         <v>30</v>
@@ -6755,7 +6945,7 @@
       </c>
       <c r="K69" s="19"/>
       <c r="L69" s="19" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6771,10 +6961,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D70" s="19" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E70" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F70" s="20" t="n">
         <v>42</v>
@@ -6791,7 +6981,7 @@
       </c>
       <c r="K70" s="19"/>
       <c r="L70" s="19" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6807,10 +6997,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D71" s="19" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E71" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F71" s="20" t="n">
         <v>77</v>
@@ -6843,10 +7033,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D72" s="19" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E72" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F72" s="20" t="n">
         <v>84</v>
@@ -6879,10 +7069,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D73" s="19" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E73" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F73" s="20" t="n">
         <v>20</v>
@@ -6899,7 +7089,7 @@
       </c>
       <c r="K73" s="19"/>
       <c r="L73" s="19" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6915,10 +7105,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D74" s="19" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E74" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F74" s="20" t="n">
         <v>30</v>
@@ -6935,7 +7125,7 @@
       </c>
       <c r="K74" s="19"/>
       <c r="L74" s="19" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6951,10 +7141,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E75" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F75" s="20" t="n">
         <v>77</v>
@@ -6987,10 +7177,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D76" s="19" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E76" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F76" s="20" t="n">
         <v>84</v>
@@ -7023,10 +7213,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D77" s="19" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E77" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F77" s="20" t="n">
         <v>25</v>
@@ -7043,7 +7233,7 @@
       </c>
       <c r="K77" s="19"/>
       <c r="L77" s="19" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7059,10 +7249,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D78" s="19" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E78" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F78" s="20" t="n">
         <v>35</v>
@@ -7079,7 +7269,7 @@
       </c>
       <c r="K78" s="19"/>
       <c r="L78" s="19" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7095,10 +7285,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D79" s="19" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E79" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F79" s="20" t="n">
         <v>63</v>
@@ -7131,10 +7321,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D80" s="19" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E80" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F80" s="20" t="n">
         <v>56</v>
@@ -7167,10 +7357,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D81" s="19" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E81" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F81" s="20" t="n">
         <v>15</v>
@@ -7203,10 +7393,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D82" s="19" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E82" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F82" s="20" t="n">
         <v>49</v>
@@ -7239,10 +7429,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D83" s="19" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E83" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F83" s="20" t="n">
         <v>35</v>
@@ -7275,10 +7465,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D84" s="19" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E84" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F84" s="20" t="n">
         <v>25</v>
@@ -7311,10 +7501,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D85" s="19" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E85" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F85" s="20" t="n">
         <v>35</v>
@@ -7347,10 +7537,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D86" s="19" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E86" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F86" s="20" t="n">
         <v>30</v>
@@ -7383,10 +7573,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D87" s="19" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E87" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F87" s="20" t="n">
         <v>25</v>
@@ -7419,10 +7609,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D88" s="19" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E88" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F88" s="20" t="n">
         <v>45</v>
@@ -7455,10 +7645,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D89" s="19" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E89" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F89" s="20" t="n">
         <v>50</v>
@@ -7491,10 +7681,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D90" s="19" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E90" s="17" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F90" s="20" t="n">
         <v>30</v>
@@ -7512,7 +7702,7 @@
         <v/>
       </c>
       <c r="K90" s="19" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="L90" s="19"/>
     </row>
@@ -7529,10 +7719,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D91" s="19" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E91" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F91" s="20" t="n">
         <v>30</v>
@@ -7565,10 +7755,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D92" s="19" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E92" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F92" s="20" t="n">
         <v>50</v>
@@ -7601,10 +7791,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D93" s="19" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E93" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F93" s="20" t="n">
         <v>55</v>
@@ -7637,10 +7827,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D94" s="19" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E94" s="17" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F94" s="20" t="n">
         <v>40</v>
@@ -7658,7 +7848,7 @@
         <v/>
       </c>
       <c r="K94" s="19" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="L94" s="19"/>
     </row>
@@ -7675,10 +7865,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D95" s="19" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E95" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F95" s="20" t="n">
         <v>35</v>
@@ -7711,10 +7901,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D96" s="19" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E96" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F96" s="20" t="n">
         <v>45</v>
@@ -7747,10 +7937,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D97" s="19" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E97" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F97" s="20" t="n">
         <v>40</v>
@@ -7783,10 +7973,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D98" s="19" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E98" s="17" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F98" s="20" t="n">
         <v>30</v>
@@ -7804,7 +7994,7 @@
         <v/>
       </c>
       <c r="K98" s="19" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="L98" s="19"/>
     </row>
@@ -7821,10 +8011,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D99" s="19" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E99" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F99" s="20" t="n">
         <v>170</v>
@@ -7843,7 +8033,7 @@
       </c>
       <c r="K99" s="19"/>
       <c r="L99" s="19" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7859,10 +8049,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D100" s="19" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E100" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F100" s="20" t="n">
         <v>220</v>
@@ -7895,10 +8085,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D101" s="19" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E101" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F101" s="20" t="n">
         <v>240</v>
@@ -7931,10 +8121,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D102" s="19" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E102" s="17" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F102" s="20"/>
       <c r="G102" s="21" t="n">
@@ -7950,10 +8140,10 @@
         <v/>
       </c>
       <c r="K102" s="19" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="L102" s="19" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7969,10 +8159,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D103" s="19" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E103" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F103" s="20" t="n">
         <v>180</v>
@@ -8005,10 +8195,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D104" s="19" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E104" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F104" s="20" t="n">
         <v>240</v>
@@ -8041,10 +8231,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D105" s="19" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E105" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F105" s="20" t="n">
         <v>280</v>
@@ -8077,10 +8267,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D106" s="19" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E106" s="17" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F106" s="20"/>
       <c r="G106" s="21" t="n">
@@ -8096,10 +8286,10 @@
         <v/>
       </c>
       <c r="K106" s="19" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="L106" s="19" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8115,10 +8305,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D107" s="19" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E107" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F107" s="20" t="n">
         <v>120</v>
@@ -8151,10 +8341,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D108" s="19" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E108" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F108" s="20" t="n">
         <v>170</v>
@@ -8187,10 +8377,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D109" s="19" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E109" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F109" s="20" t="n">
         <v>280</v>
@@ -8223,10 +8413,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D110" s="19" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E110" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F110" s="20" t="n">
         <v>270</v>
@@ -8259,10 +8449,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D111" s="19" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E111" s="17" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F111" s="20"/>
       <c r="G111" s="21" t="n">
@@ -8278,10 +8468,10 @@
         <v/>
       </c>
       <c r="K111" s="19" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="L111" s="19" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8297,10 +8487,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D112" s="19" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E112" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F112" s="20" t="n">
         <v>120</v>
@@ -8333,10 +8523,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D113" s="19" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E113" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F113" s="20" t="n">
         <v>170</v>
@@ -8369,10 +8559,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D114" s="19" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E114" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F114" s="20" t="n">
         <v>270</v>
@@ -8405,10 +8595,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D115" s="19" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E115" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F115" s="20" t="n">
         <v>270</v>
@@ -8441,10 +8631,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D116" s="19" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E116" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F116" s="20" t="n">
         <v>270</v>
@@ -8477,10 +8667,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D117" s="19" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E117" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F117" s="20" t="n">
         <v>65</v>
@@ -8513,10 +8703,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D118" s="19" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E118" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F118" s="20" t="n">
         <v>145</v>
@@ -8549,10 +8739,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D119" s="19" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E119" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F119" s="20" t="n">
         <v>115</v>
@@ -8585,10 +8775,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D120" s="19" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E120" s="17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F120" s="20" t="n">
         <v>67.5</v>
@@ -8621,10 +8811,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D121" s="19" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E121" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F121" s="20" t="n">
         <v>150</v>
@@ -8657,10 +8847,10 @@
         <v>Beine hinten</v>
       </c>
       <c r="D122" s="19" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E122" s="17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F122" s="20" t="n">
         <v>140</v>
@@ -18640,7 +18830,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -18662,7 +18852,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -18684,7 +18874,7 @@
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -18706,7 +18896,7 @@
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B5" s="16" t="n">
         <v>1</v>
@@ -18757,29 +18947,29 @@
         <v>16</v>
       </c>
       <c r="R5" s="16" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="str">
         <f aca="false">IF(Übungen!$A4="","",Übungen!$A4)</f>
-        <v>Adduktion</v>
-      </c>
-      <c r="B6" s="31" t="n">
+        <v>Hackenschmidt-Kniebeuge</v>
+      </c>
+      <c r="B6" s="31" t="str">
         <f aca="false">IF($A6="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A6,Log!$B$4:$B$503,B$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A6,Log!$B$4:$B$503,B$5,Log!$E$4:$E$503,"A")))</f>
-        <v>4117.5</v>
-      </c>
-      <c r="C6" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C6" s="31" t="str">
         <f aca="false">IF($A6="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A6,Log!$B$4:$B$503,C$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A6,Log!$B$4:$B$503,C$5,Log!$E$4:$E$503,"A")))</f>
-        <v>5490</v>
-      </c>
-      <c r="D6" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D6" s="31" t="str">
         <f aca="false">IF($A6="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A6,Log!$B$4:$B$503,D$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A6,Log!$B$4:$B$503,D$5,Log!$E$4:$E$503,"A")))</f>
-        <v>5337.5</v>
-      </c>
-      <c r="E6" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E6" s="31" t="str">
         <f aca="false">IF($A6="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A6,Log!$B$4:$B$503,E$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A6,Log!$B$4:$B$503,E$5,Log!$E$4:$E$503,"A")))</f>
-        <v>6862.5</v>
+        <v/>
       </c>
       <c r="F6" s="31" t="str">
         <f aca="false">IF($A6="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A6,Log!$B$4:$B$503,F$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A6,Log!$B$4:$B$503,F$5,Log!$E$4:$E$503,"A")))</f>
@@ -18829,31 +19019,31 @@
         <f aca="false">IF($A6="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A6,Log!$B$4:$B$503,Q$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A6,Log!$B$4:$B$503,Q$5,Log!$E$4:$E$503,"A")))</f>
         <v/>
       </c>
-      <c r="R6" s="32" t="n">
+      <c r="R6" s="32" t="str">
         <f aca="false">IF(COUNT(B6:Q6)=0,"",SUM(B6:Q6))</f>
-        <v>21807.5</v>
+        <v/>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="str">
         <f aca="false">IF(Übungen!$A5="","",Übungen!$A5)</f>
-        <v>Beinstrecker</v>
+        <v>Split Squat</v>
       </c>
       <c r="B7" s="34" t="n">
         <f aca="false">IF($A7="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A7,Log!$B$4:$B$503,B$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A7,Log!$B$4:$B$503,B$5,Log!$E$4:$E$503,"A")))</f>
-        <v>1205</v>
+        <v>1610</v>
       </c>
       <c r="C7" s="34" t="n">
         <f aca="false">IF($A7="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A7,Log!$B$4:$B$503,C$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A7,Log!$B$4:$B$503,C$5,Log!$E$4:$E$503,"A")))</f>
-        <v>1630</v>
+        <v>1575</v>
       </c>
       <c r="D7" s="34" t="n">
         <f aca="false">IF($A7="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A7,Log!$B$4:$B$503,D$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A7,Log!$B$4:$B$503,D$5,Log!$E$4:$E$503,"A")))</f>
-        <v>1430</v>
+        <v>2275</v>
       </c>
       <c r="E7" s="34" t="n">
         <f aca="false">IF($A7="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A7,Log!$B$4:$B$503,E$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A7,Log!$B$4:$B$503,E$5,Log!$E$4:$E$503,"A")))</f>
-        <v>1600</v>
+        <v>1640</v>
       </c>
       <c r="F7" s="34" t="str">
         <f aca="false">IF($A7="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A7,Log!$B$4:$B$503,F$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A7,Log!$B$4:$B$503,F$5,Log!$E$4:$E$503,"A")))</f>
@@ -18905,29 +19095,29 @@
       </c>
       <c r="R7" s="32" t="n">
         <f aca="false">IF(COUNT(B7:Q7)=0,"",SUM(B7:Q7))</f>
-        <v>5865</v>
+        <v>7100</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="str">
         <f aca="false">IF(Übungen!$A6="","",Übungen!$A6)</f>
-        <v>Split Squat</v>
+        <v>Beinstrecker</v>
       </c>
       <c r="B8" s="31" t="n">
         <f aca="false">IF($A8="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A8,Log!$B$4:$B$503,B$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A8,Log!$B$4:$B$503,B$5,Log!$E$4:$E$503,"A")))</f>
-        <v>1610</v>
+        <v>1205</v>
       </c>
       <c r="C8" s="31" t="n">
         <f aca="false">IF($A8="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A8,Log!$B$4:$B$503,C$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A8,Log!$B$4:$B$503,C$5,Log!$E$4:$E$503,"A")))</f>
-        <v>1575</v>
+        <v>1630</v>
       </c>
       <c r="D8" s="31" t="n">
         <f aca="false">IF($A8="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A8,Log!$B$4:$B$503,D$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A8,Log!$B$4:$B$503,D$5,Log!$E$4:$E$503,"A")))</f>
-        <v>2275</v>
+        <v>1430</v>
       </c>
       <c r="E8" s="31" t="n">
         <f aca="false">IF($A8="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A8,Log!$B$4:$B$503,E$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A8,Log!$B$4:$B$503,E$5,Log!$E$4:$E$503,"A")))</f>
-        <v>1640</v>
+        <v>1600</v>
       </c>
       <c r="F8" s="31" t="str">
         <f aca="false">IF($A8="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A8,Log!$B$4:$B$503,F$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A8,Log!$B$4:$B$503,F$5,Log!$E$4:$E$503,"A")))</f>
@@ -18979,29 +19169,29 @@
       </c>
       <c r="R8" s="32" t="n">
         <f aca="false">IF(COUNT(B8:Q8)=0,"",SUM(B8:Q8))</f>
-        <v>7100</v>
+        <v>5865</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="str">
         <f aca="false">IF(Übungen!$A7="","",Übungen!$A7)</f>
-        <v>Lunges</v>
-      </c>
-      <c r="B9" s="34" t="str">
+        <v>Adduktion</v>
+      </c>
+      <c r="B9" s="34" t="n">
         <f aca="false">IF($A9="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A9,Log!$B$4:$B$503,B$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A9,Log!$B$4:$B$503,B$5,Log!$E$4:$E$503,"A")))</f>
-        <v/>
-      </c>
-      <c r="C9" s="34" t="str">
+        <v>4117.5</v>
+      </c>
+      <c r="C9" s="34" t="n">
         <f aca="false">IF($A9="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A9,Log!$B$4:$B$503,C$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A9,Log!$B$4:$B$503,C$5,Log!$E$4:$E$503,"A")))</f>
-        <v/>
-      </c>
-      <c r="D9" s="34" t="str">
+        <v>5490</v>
+      </c>
+      <c r="D9" s="34" t="n">
         <f aca="false">IF($A9="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A9,Log!$B$4:$B$503,D$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A9,Log!$B$4:$B$503,D$5,Log!$E$4:$E$503,"A")))</f>
-        <v/>
-      </c>
-      <c r="E9" s="34" t="str">
+        <v>5337.5</v>
+      </c>
+      <c r="E9" s="34" t="n">
         <f aca="false">IF($A9="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A9,Log!$B$4:$B$503,E$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A9,Log!$B$4:$B$503,E$5,Log!$E$4:$E$503,"A")))</f>
-        <v/>
+        <v>6862.5</v>
       </c>
       <c r="F9" s="34" t="str">
         <f aca="false">IF($A9="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A9,Log!$B$4:$B$503,F$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A9,Log!$B$4:$B$503,F$5,Log!$E$4:$E$503,"A")))</f>
@@ -19051,31 +19241,31 @@
         <f aca="false">IF($A9="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A9,Log!$B$4:$B$503,Q$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A9,Log!$B$4:$B$503,Q$5,Log!$E$4:$E$503,"A")))</f>
         <v/>
       </c>
-      <c r="R9" s="32" t="str">
+      <c r="R9" s="32" t="n">
         <f aca="false">IF(COUNT(B9:Q9)=0,"",SUM(B9:Q9))</f>
-        <v/>
+        <v>21807.5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="30" t="str">
         <f aca="false">IF(Übungen!$A8="","",Übungen!$A8)</f>
-        <v>Kickback</v>
-      </c>
-      <c r="B10" s="31" t="n">
+        <v>Rumänisches Kreuzheben</v>
+      </c>
+      <c r="B10" s="31" t="str">
         <f aca="false">IF($A10="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A10,Log!$B$4:$B$503,B$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A10,Log!$B$4:$B$503,B$5,Log!$E$4:$E$503,"A")))</f>
-        <v>1974</v>
-      </c>
-      <c r="C10" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C10" s="31" t="str">
         <f aca="false">IF($A10="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A10,Log!$B$4:$B$503,C$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A10,Log!$B$4:$B$503,C$5,Log!$E$4:$E$503,"A")))</f>
-        <v>1274</v>
-      </c>
-      <c r="D10" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D10" s="31" t="str">
         <f aca="false">IF($A10="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A10,Log!$B$4:$B$503,D$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A10,Log!$B$4:$B$503,D$5,Log!$E$4:$E$503,"A")))</f>
-        <v>2086</v>
-      </c>
-      <c r="E10" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E10" s="31" t="str">
         <f aca="false">IF($A10="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A10,Log!$B$4:$B$503,E$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A10,Log!$B$4:$B$503,E$5,Log!$E$4:$E$503,"A")))</f>
-        <v>1785</v>
+        <v/>
       </c>
       <c r="F10" s="31" t="str">
         <f aca="false">IF($A10="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A10,Log!$B$4:$B$503,F$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A10,Log!$B$4:$B$503,F$5,Log!$E$4:$E$503,"A")))</f>
@@ -19125,31 +19315,31 @@
         <f aca="false">IF($A10="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A10,Log!$B$4:$B$503,Q$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A10,Log!$B$4:$B$503,Q$5,Log!$E$4:$E$503,"A")))</f>
         <v/>
       </c>
-      <c r="R10" s="32" t="n">
+      <c r="R10" s="32" t="str">
         <f aca="false">IF(COUNT(B10:Q10)=0,"",SUM(B10:Q10))</f>
-        <v>7119</v>
+        <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="str">
         <f aca="false">IF(Übungen!$A9="","",Übungen!$A9)</f>
-        <v>Seitliche Kickbacks</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="B11" s="34" t="n">
         <f aca="false">IF($A11="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A11,Log!$B$4:$B$503,B$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A11,Log!$B$4:$B$503,B$5,Log!$E$4:$E$503,"A")))</f>
-        <v>1078</v>
+        <v>4560</v>
       </c>
       <c r="C11" s="34" t="n">
         <f aca="false">IF($A11="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A11,Log!$B$4:$B$503,C$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A11,Log!$B$4:$B$503,C$5,Log!$E$4:$E$503,"A")))</f>
-        <v>975</v>
-      </c>
-      <c r="D11" s="34" t="str">
+        <v>4080</v>
+      </c>
+      <c r="D11" s="34" t="n">
         <f aca="false">IF($A11="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A11,Log!$B$4:$B$503,D$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A11,Log!$B$4:$B$503,D$5,Log!$E$4:$E$503,"A")))</f>
-        <v/>
-      </c>
-      <c r="E11" s="34" t="str">
+        <v>4940</v>
+      </c>
+      <c r="E11" s="34" t="n">
         <f aca="false">IF($A11="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A11,Log!$B$4:$B$503,E$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A11,Log!$B$4:$B$503,E$5,Log!$E$4:$E$503,"A")))</f>
-        <v/>
+        <v>6480</v>
       </c>
       <c r="F11" s="34" t="str">
         <f aca="false">IF($A11="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A11,Log!$B$4:$B$503,F$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A11,Log!$B$4:$B$503,F$5,Log!$E$4:$E$503,"A")))</f>
@@ -19201,7 +19391,7 @@
       </c>
       <c r="R11" s="32" t="n">
         <f aca="false">IF(COUNT(B11:Q11)=0,"",SUM(B11:Q11))</f>
-        <v>2053</v>
+        <v>20060</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19281,23 +19471,23 @@
     <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="str">
         <f aca="false">IF(Übungen!$A11="","",Übungen!$A11)</f>
-        <v>Hip Thrust</v>
+        <v>Seitliche Kickbacks</v>
       </c>
       <c r="B13" s="34" t="n">
         <f aca="false">IF($A13="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A13,Log!$B$4:$B$503,B$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A13,Log!$B$4:$B$503,B$5,Log!$E$4:$E$503,"A")))</f>
-        <v>4560</v>
+        <v>1078</v>
       </c>
       <c r="C13" s="34" t="n">
         <f aca="false">IF($A13="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A13,Log!$B$4:$B$503,C$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A13,Log!$B$4:$B$503,C$5,Log!$E$4:$E$503,"A")))</f>
-        <v>4080</v>
-      </c>
-      <c r="D13" s="34" t="n">
+        <v>975</v>
+      </c>
+      <c r="D13" s="34" t="str">
         <f aca="false">IF($A13="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A13,Log!$B$4:$B$503,D$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A13,Log!$B$4:$B$503,D$5,Log!$E$4:$E$503,"A")))</f>
-        <v>4940</v>
-      </c>
-      <c r="E13" s="34" t="n">
+        <v/>
+      </c>
+      <c r="E13" s="34" t="str">
         <f aca="false">IF($A13="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A13,Log!$B$4:$B$503,E$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A13,Log!$B$4:$B$503,E$5,Log!$E$4:$E$503,"A")))</f>
-        <v>6480</v>
+        <v/>
       </c>
       <c r="F13" s="34" t="str">
         <f aca="false">IF($A13="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A13,Log!$B$4:$B$503,F$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A13,Log!$B$4:$B$503,F$5,Log!$E$4:$E$503,"A")))</f>
@@ -19349,7 +19539,7 @@
       </c>
       <c r="R13" s="32" t="n">
         <f aca="false">IF(COUNT(B13:Q13)=0,"",SUM(B13:Q13))</f>
-        <v>20060</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19429,7 +19619,7 @@
     <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="33" t="str">
         <f aca="false">IF(Übungen!$A13="","",Übungen!$A13)</f>
-        <v/>
+        <v>Lunges</v>
       </c>
       <c r="B15" s="34" t="str">
         <f aca="false">IF($A15="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A15,Log!$B$4:$B$503,B$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A15,Log!$B$4:$B$503,B$5,Log!$E$4:$E$503,"A")))</f>
@@ -19503,23 +19693,23 @@
     <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="30" t="str">
         <f aca="false">IF(Übungen!$A14="","",Übungen!$A14)</f>
-        <v/>
-      </c>
-      <c r="B16" s="31" t="str">
+        <v>Kickback</v>
+      </c>
+      <c r="B16" s="31" t="n">
         <f aca="false">IF($A16="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A16,Log!$B$4:$B$503,B$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A16,Log!$B$4:$B$503,B$5,Log!$E$4:$E$503,"A")))</f>
-        <v/>
-      </c>
-      <c r="C16" s="31" t="str">
+        <v>1974</v>
+      </c>
+      <c r="C16" s="31" t="n">
         <f aca="false">IF($A16="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A16,Log!$B$4:$B$503,C$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A16,Log!$B$4:$B$503,C$5,Log!$E$4:$E$503,"A")))</f>
-        <v/>
-      </c>
-      <c r="D16" s="31" t="str">
+        <v>1274</v>
+      </c>
+      <c r="D16" s="31" t="n">
         <f aca="false">IF($A16="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A16,Log!$B$4:$B$503,D$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A16,Log!$B$4:$B$503,D$5,Log!$E$4:$E$503,"A")))</f>
-        <v/>
-      </c>
-      <c r="E16" s="31" t="str">
+        <v>2086</v>
+      </c>
+      <c r="E16" s="31" t="n">
         <f aca="false">IF($A16="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A16,Log!$B$4:$B$503,E$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A16,Log!$B$4:$B$503,E$5,Log!$E$4:$E$503,"A")))</f>
-        <v/>
+        <v>1785</v>
       </c>
       <c r="F16" s="31" t="str">
         <f aca="false">IF($A16="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A16,Log!$B$4:$B$503,F$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A16,Log!$B$4:$B$503,F$5,Log!$E$4:$E$503,"A")))</f>
@@ -19569,9 +19759,9 @@
         <f aca="false">IF($A16="","",IF(SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A16,Log!$B$4:$B$503,Q$5,Log!$E$4:$E$503,"A")=0,"",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A16,Log!$B$4:$B$503,Q$5,Log!$E$4:$E$503,"A")))</f>
         <v/>
       </c>
-      <c r="R16" s="32" t="str">
+      <c r="R16" s="32" t="n">
         <f aca="false">IF(COUNT(B16:Q16)=0,"",SUM(B16:Q16))</f>
-        <v/>
+        <v>7119</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19798,7 +19988,7 @@
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -19820,7 +20010,7 @@
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="16" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B23" s="16" t="n">
         <v>1</v>
@@ -19871,29 +20061,29 @@
         <v>16</v>
       </c>
       <c r="R23" s="16" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="30" t="str">
         <f aca="false">IF(Übungen!$A4="","",Übungen!$A4)</f>
-        <v>Adduktion</v>
-      </c>
-      <c r="B24" s="35" t="n">
+        <v>Hackenschmidt-Kniebeuge</v>
+      </c>
+      <c r="B24" s="35" t="str">
         <f aca="false">IF($A24="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A24)*(Log!$B$4:$B$503=B$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A24)*(Log!$B$4:$B$503=B$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>152.5</v>
-      </c>
-      <c r="C24" s="35" t="n">
+        <v/>
+      </c>
+      <c r="C24" s="35" t="str">
         <f aca="false">IF($A24="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A24)*(Log!$B$4:$B$503=C$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A24)*(Log!$B$4:$B$503=C$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>152.5</v>
-      </c>
-      <c r="D24" s="35" t="n">
+        <v/>
+      </c>
+      <c r="D24" s="35" t="str">
         <f aca="false">IF($A24="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A24)*(Log!$B$4:$B$503=D$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A24)*(Log!$B$4:$B$503=D$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>152.5</v>
-      </c>
-      <c r="E24" s="35" t="n">
+        <v/>
+      </c>
+      <c r="E24" s="35" t="str">
         <f aca="false">IF($A24="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A24)*(Log!$B$4:$B$503=E$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A24)*(Log!$B$4:$B$503=E$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>152.5</v>
+        <v/>
       </c>
       <c r="F24" s="35" t="str">
         <f aca="false">IF($A24="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A24)*(Log!$B$4:$B$503=F$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A24)*(Log!$B$4:$B$503=F$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
@@ -19943,27 +20133,27 @@
         <f aca="false">IF($A24="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A24)*(Log!$B$4:$B$503=Q$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A24)*(Log!$B$4:$B$503=Q$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
         <v/>
       </c>
-      <c r="R24" s="36" t="n">
+      <c r="R24" s="36" t="str">
         <f aca="false">IF(COUNT(B24:Q24)=0,"",MAX(B24:Q24))</f>
-        <v>152.5</v>
+        <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="33" t="str">
         <f aca="false">IF(Übungen!$A5="","",Übungen!$A5)</f>
-        <v>Beinstrecker</v>
+        <v>Split Squat</v>
       </c>
       <c r="B25" s="37" t="n">
         <f aca="false">IF($A25="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A25)*(Log!$B$4:$B$503=B$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A25)*(Log!$B$4:$B$503=B$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C25" s="37" t="n">
         <f aca="false">IF($A25="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A25)*(Log!$B$4:$B$503=C$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A25)*(Log!$B$4:$B$503=C$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="D25" s="37" t="n">
         <f aca="false">IF($A25="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A25)*(Log!$B$4:$B$503=D$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A25)*(Log!$B$4:$B$503=D$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="E25" s="37" t="n">
         <f aca="false">IF($A25="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A25)*(Log!$B$4:$B$503=E$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A25)*(Log!$B$4:$B$503=E$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
@@ -20019,25 +20209,25 @@
       </c>
       <c r="R25" s="36" t="n">
         <f aca="false">IF(COUNT(B25:Q25)=0,"",MAX(B25:Q25))</f>
-        <v>85</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="30" t="str">
         <f aca="false">IF(Übungen!$A6="","",Übungen!$A6)</f>
-        <v>Split Squat</v>
+        <v>Beinstrecker</v>
       </c>
       <c r="B26" s="35" t="n">
         <f aca="false">IF($A26="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A26)*(Log!$B$4:$B$503=B$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A26)*(Log!$B$4:$B$503=B$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="C26" s="35" t="n">
         <f aca="false">IF($A26="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A26)*(Log!$B$4:$B$503=C$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A26)*(Log!$B$4:$B$503=C$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="D26" s="35" t="n">
         <f aca="false">IF($A26="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A26)*(Log!$B$4:$B$503=D$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A26)*(Log!$B$4:$B$503=D$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E26" s="35" t="n">
         <f aca="false">IF($A26="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A26)*(Log!$B$4:$B$503=E$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A26)*(Log!$B$4:$B$503=E$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
@@ -20093,29 +20283,29 @@
       </c>
       <c r="R26" s="36" t="n">
         <f aca="false">IF(COUNT(B26:Q26)=0,"",MAX(B26:Q26))</f>
-        <v>105</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="33" t="str">
         <f aca="false">IF(Übungen!$A7="","",Übungen!$A7)</f>
-        <v>Lunges</v>
+        <v>Adduktion</v>
       </c>
       <c r="B27" s="37" t="n">
         <f aca="false">IF($A27="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A27)*(Log!$B$4:$B$503=B$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A27)*(Log!$B$4:$B$503=B$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>10</v>
+        <v>152.5</v>
       </c>
       <c r="C27" s="37" t="n">
         <f aca="false">IF($A27="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A27)*(Log!$B$4:$B$503=C$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A27)*(Log!$B$4:$B$503=C$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>16</v>
+        <v>152.5</v>
       </c>
       <c r="D27" s="37" t="n">
         <f aca="false">IF($A27="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A27)*(Log!$B$4:$B$503=D$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A27)*(Log!$B$4:$B$503=D$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>18</v>
-      </c>
-      <c r="E27" s="37" t="str">
+        <v>152.5</v>
+      </c>
+      <c r="E27" s="37" t="n">
         <f aca="false">IF($A27="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A27)*(Log!$B$4:$B$503=E$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A27)*(Log!$B$4:$B$503=E$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v/>
+        <v>152.5</v>
       </c>
       <c r="F27" s="37" t="str">
         <f aca="false">IF($A27="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A27)*(Log!$B$4:$B$503=F$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A27)*(Log!$B$4:$B$503=F$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
@@ -20167,29 +20357,29 @@
       </c>
       <c r="R27" s="36" t="n">
         <f aca="false">IF(COUNT(B27:Q27)=0,"",MAX(B27:Q27))</f>
-        <v>18</v>
+        <v>152.5</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="30" t="str">
         <f aca="false">IF(Übungen!$A8="","",Übungen!$A8)</f>
-        <v>Kickback</v>
-      </c>
-      <c r="B28" s="35" t="n">
+        <v>Rumänisches Kreuzheben</v>
+      </c>
+      <c r="B28" s="35" t="str">
         <f aca="false">IF($A28="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A28)*(Log!$B$4:$B$503=B$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A28)*(Log!$B$4:$B$503=B$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>77</v>
-      </c>
-      <c r="C28" s="35" t="n">
+        <v/>
+      </c>
+      <c r="C28" s="35" t="str">
         <f aca="false">IF($A28="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A28)*(Log!$B$4:$B$503=C$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A28)*(Log!$B$4:$B$503=C$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>84</v>
-      </c>
-      <c r="D28" s="35" t="n">
+        <v/>
+      </c>
+      <c r="D28" s="35" t="str">
         <f aca="false">IF($A28="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A28)*(Log!$B$4:$B$503=D$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A28)*(Log!$B$4:$B$503=D$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>84</v>
-      </c>
-      <c r="E28" s="35" t="n">
+        <v/>
+      </c>
+      <c r="E28" s="35" t="str">
         <f aca="false">IF($A28="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A28)*(Log!$B$4:$B$503=E$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A28)*(Log!$B$4:$B$503=E$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>63</v>
+        <v/>
       </c>
       <c r="F28" s="35" t="str">
         <f aca="false">IF($A28="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A28)*(Log!$B$4:$B$503=F$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A28)*(Log!$B$4:$B$503=F$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
@@ -20239,31 +20429,31 @@
         <f aca="false">IF($A28="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A28)*(Log!$B$4:$B$503=Q$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A28)*(Log!$B$4:$B$503=Q$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
         <v/>
       </c>
-      <c r="R28" s="36" t="n">
+      <c r="R28" s="36" t="str">
         <f aca="false">IF(COUNT(B28:Q28)=0,"",MAX(B28:Q28))</f>
-        <v>84</v>
+        <v/>
       </c>
     </row>
     <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="33" t="str">
         <f aca="false">IF(Übungen!$A9="","",Übungen!$A9)</f>
-        <v>Seitliche Kickbacks</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="B29" s="37" t="n">
         <f aca="false">IF($A29="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A29)*(Log!$B$4:$B$503=B$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A29)*(Log!$B$4:$B$503=B$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>49</v>
+        <v>240</v>
       </c>
       <c r="C29" s="37" t="n">
         <f aca="false">IF($A29="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A29)*(Log!$B$4:$B$503=C$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A29)*(Log!$B$4:$B$503=C$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>35</v>
-      </c>
-      <c r="D29" s="37" t="str">
+        <v>280</v>
+      </c>
+      <c r="D29" s="37" t="n">
         <f aca="false">IF($A29="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A29)*(Log!$B$4:$B$503=D$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A29)*(Log!$B$4:$B$503=D$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v/>
-      </c>
-      <c r="E29" s="37" t="str">
+        <v>280</v>
+      </c>
+      <c r="E29" s="37" t="n">
         <f aca="false">IF($A29="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A29)*(Log!$B$4:$B$503=E$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A29)*(Log!$B$4:$B$503=E$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v/>
+        <v>270</v>
       </c>
       <c r="F29" s="37" t="str">
         <f aca="false">IF($A29="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A29)*(Log!$B$4:$B$503=F$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A29)*(Log!$B$4:$B$503=F$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
@@ -20315,7 +20505,7 @@
       </c>
       <c r="R29" s="36" t="n">
         <f aca="false">IF(COUNT(B29:Q29)=0,"",MAX(B29:Q29))</f>
-        <v>49</v>
+        <v>280</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20395,23 +20585,23 @@
     <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="33" t="str">
         <f aca="false">IF(Übungen!$A11="","",Übungen!$A11)</f>
-        <v>Hip Thrust</v>
+        <v>Seitliche Kickbacks</v>
       </c>
       <c r="B31" s="37" t="n">
         <f aca="false">IF($A31="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A31)*(Log!$B$4:$B$503=B$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A31)*(Log!$B$4:$B$503=B$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>240</v>
+        <v>49</v>
       </c>
       <c r="C31" s="37" t="n">
         <f aca="false">IF($A31="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A31)*(Log!$B$4:$B$503=C$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A31)*(Log!$B$4:$B$503=C$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>280</v>
-      </c>
-      <c r="D31" s="37" t="n">
+        <v>35</v>
+      </c>
+      <c r="D31" s="37" t="str">
         <f aca="false">IF($A31="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A31)*(Log!$B$4:$B$503=D$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A31)*(Log!$B$4:$B$503=D$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>280</v>
-      </c>
-      <c r="E31" s="37" t="n">
+        <v/>
+      </c>
+      <c r="E31" s="37" t="str">
         <f aca="false">IF($A31="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A31)*(Log!$B$4:$B$503=E$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A31)*(Log!$B$4:$B$503=E$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>270</v>
+        <v/>
       </c>
       <c r="F31" s="37" t="str">
         <f aca="false">IF($A31="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A31)*(Log!$B$4:$B$503=F$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A31)*(Log!$B$4:$B$503=F$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
@@ -20463,7 +20653,7 @@
       </c>
       <c r="R31" s="36" t="n">
         <f aca="false">IF(COUNT(B31:Q31)=0,"",MAX(B31:Q31))</f>
-        <v>280</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20543,19 +20733,19 @@
     <row r="33" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="33" t="str">
         <f aca="false">IF(Übungen!$A13="","",Übungen!$A13)</f>
-        <v/>
-      </c>
-      <c r="B33" s="37" t="str">
+        <v>Lunges</v>
+      </c>
+      <c r="B33" s="37" t="n">
         <f aca="false">IF($A33="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A33)*(Log!$B$4:$B$503=B$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A33)*(Log!$B$4:$B$503=B$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v/>
-      </c>
-      <c r="C33" s="37" t="str">
+        <v>10</v>
+      </c>
+      <c r="C33" s="37" t="n">
         <f aca="false">IF($A33="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A33)*(Log!$B$4:$B$503=C$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A33)*(Log!$B$4:$B$503=C$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v/>
-      </c>
-      <c r="D33" s="37" t="str">
+        <v>16</v>
+      </c>
+      <c r="D33" s="37" t="n">
         <f aca="false">IF($A33="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A33)*(Log!$B$4:$B$503=D$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A33)*(Log!$B$4:$B$503=D$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="E33" s="37" t="str">
         <f aca="false">IF($A33="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A33)*(Log!$B$4:$B$503=E$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A33)*(Log!$B$4:$B$503=E$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
@@ -20609,31 +20799,31 @@
         <f aca="false">IF($A33="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A33)*(Log!$B$4:$B$503=Q$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A33)*(Log!$B$4:$B$503=Q$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
         <v/>
       </c>
-      <c r="R33" s="36" t="str">
+      <c r="R33" s="36" t="n">
         <f aca="false">IF(COUNT(B33:Q33)=0,"",MAX(B33:Q33))</f>
-        <v/>
+        <v>18</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="30" t="str">
         <f aca="false">IF(Übungen!$A14="","",Übungen!$A14)</f>
-        <v/>
-      </c>
-      <c r="B34" s="35" t="str">
+        <v>Kickback</v>
+      </c>
+      <c r="B34" s="35" t="n">
         <f aca="false">IF($A34="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A34)*(Log!$B$4:$B$503=B$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A34)*(Log!$B$4:$B$503=B$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v/>
-      </c>
-      <c r="C34" s="35" t="str">
+        <v>77</v>
+      </c>
+      <c r="C34" s="35" t="n">
         <f aca="false">IF($A34="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A34)*(Log!$B$4:$B$503=C$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A34)*(Log!$B$4:$B$503=C$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v/>
-      </c>
-      <c r="D34" s="35" t="str">
+        <v>84</v>
+      </c>
+      <c r="D34" s="35" t="n">
         <f aca="false">IF($A34="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A34)*(Log!$B$4:$B$503=D$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A34)*(Log!$B$4:$B$503=D$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v/>
-      </c>
-      <c r="E34" s="35" t="str">
+        <v>84</v>
+      </c>
+      <c r="E34" s="35" t="n">
         <f aca="false">IF($A34="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A34)*(Log!$B$4:$B$503=E$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A34)*(Log!$B$4:$B$503=E$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v/>
+        <v>63</v>
       </c>
       <c r="F34" s="35" t="str">
         <f aca="false">IF($A34="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A34)*(Log!$B$4:$B$503=F$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A34)*(Log!$B$4:$B$503=F$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
@@ -20683,9 +20873,9 @@
         <f aca="false">IF($A34="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A34)*(Log!$B$4:$B$503=Q$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A34)*(Log!$B$4:$B$503=Q$23)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
         <v/>
       </c>
-      <c r="R34" s="36" t="str">
+      <c r="R34" s="36" t="n">
         <f aca="false">IF(COUNT(B34:Q34)=0,"",MAX(B34:Q34))</f>
-        <v/>
+        <v>84</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20912,7 +21102,7 @@
     </row>
     <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -20934,7 +21124,7 @@
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="16" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B41" s="16" t="n">
         <v>1</v>
@@ -20985,29 +21175,29 @@
         <v>16</v>
       </c>
       <c r="R41" s="16" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="30" t="str">
         <f aca="false">IF(Übungen!$A4="","",Übungen!$A4)</f>
-        <v>Adduktion</v>
-      </c>
-      <c r="B42" s="35" t="n">
+        <v>Hackenschmidt-Kniebeuge</v>
+      </c>
+      <c r="B42" s="35" t="str">
         <f aca="false">IF($A42="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A42)*(Log!$B$4:$B$503=B$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A42)*(Log!$B$4:$B$503=B$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v>238.916666666667</v>
-      </c>
-      <c r="C42" s="35" t="n">
+        <v/>
+      </c>
+      <c r="C42" s="35" t="str">
         <f aca="false">IF($A42="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A42)*(Log!$B$4:$B$503=C$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A42)*(Log!$B$4:$B$503=C$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v>254.166666666667</v>
-      </c>
-      <c r="D42" s="35" t="n">
+        <v/>
+      </c>
+      <c r="D42" s="35" t="str">
         <f aca="false">IF($A42="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A42)*(Log!$B$4:$B$503=D$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A42)*(Log!$B$4:$B$503=D$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v>264.333333333333</v>
-      </c>
-      <c r="E42" s="35" t="n">
+        <v/>
+      </c>
+      <c r="E42" s="35" t="str">
         <f aca="false">IF($A42="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A42)*(Log!$B$4:$B$503=E$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A42)*(Log!$B$4:$B$503=E$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v>279.583333333333</v>
+        <v/>
       </c>
       <c r="F42" s="35" t="str">
         <f aca="false">IF($A42="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A42)*(Log!$B$4:$B$503=F$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A42)*(Log!$B$4:$B$503=F$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
@@ -21057,31 +21247,31 @@
         <f aca="false">IF($A42="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A42)*(Log!$B$4:$B$503=Q$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A42)*(Log!$B$4:$B$503=Q$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
         <v/>
       </c>
-      <c r="R42" s="36" t="n">
+      <c r="R42" s="36" t="str">
         <f aca="false">IF(COUNT(B42:Q42)=0,"",MAX(B42:Q42))</f>
-        <v>279.583333333333</v>
+        <v/>
       </c>
     </row>
     <row r="43" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="33" t="str">
         <f aca="false">IF(Übungen!$A5="","",Übungen!$A5)</f>
-        <v>Beinstrecker</v>
+        <v>Split Squat</v>
       </c>
       <c r="B43" s="37" t="n">
         <f aca="false">IF($A43="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A43)*(Log!$B$4:$B$503=B$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A43)*(Log!$B$4:$B$503=B$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v>100</v>
+        <v>116.666666666667</v>
       </c>
       <c r="C43" s="37" t="n">
         <f aca="false">IF($A43="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A43)*(Log!$B$4:$B$503=C$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A43)*(Log!$B$4:$B$503=C$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="D43" s="37" t="n">
         <f aca="false">IF($A43="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A43)*(Log!$B$4:$B$503=D$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A43)*(Log!$B$4:$B$503=D$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v>107.666666666667</v>
+        <v>123.5</v>
       </c>
       <c r="E43" s="37" t="n">
         <f aca="false">IF($A43="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A43)*(Log!$B$4:$B$503=E$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A43)*(Log!$B$4:$B$503=E$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v>112</v>
+        <v>101.333333333333</v>
       </c>
       <c r="F43" s="37" t="str">
         <f aca="false">IF($A43="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A43)*(Log!$B$4:$B$503=F$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A43)*(Log!$B$4:$B$503=F$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
@@ -21133,29 +21323,29 @@
       </c>
       <c r="R43" s="36" t="n">
         <f aca="false">IF(COUNT(B43:Q43)=0,"",MAX(B43:Q43))</f>
-        <v>112</v>
+        <v>123.5</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="30" t="str">
         <f aca="false">IF(Übungen!$A6="","",Übungen!$A6)</f>
-        <v>Split Squat</v>
+        <v>Beinstrecker</v>
       </c>
       <c r="B44" s="35" t="n">
         <f aca="false">IF($A44="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A44)*(Log!$B$4:$B$503=B$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A44)*(Log!$B$4:$B$503=B$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v>116.666666666667</v>
+        <v>100</v>
       </c>
       <c r="C44" s="35" t="n">
         <f aca="false">IF($A44="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A44)*(Log!$B$4:$B$503=C$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A44)*(Log!$B$4:$B$503=C$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="D44" s="35" t="n">
         <f aca="false">IF($A44="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A44)*(Log!$B$4:$B$503=D$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A44)*(Log!$B$4:$B$503=D$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v>123.5</v>
+        <v>107.666666666667</v>
       </c>
       <c r="E44" s="35" t="n">
         <f aca="false">IF($A44="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A44)*(Log!$B$4:$B$503=E$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A44)*(Log!$B$4:$B$503=E$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v>101.333333333333</v>
+        <v>112</v>
       </c>
       <c r="F44" s="35" t="str">
         <f aca="false">IF($A44="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A44)*(Log!$B$4:$B$503=F$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A44)*(Log!$B$4:$B$503=F$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
@@ -21207,29 +21397,29 @@
       </c>
       <c r="R44" s="36" t="n">
         <f aca="false">IF(COUNT(B44:Q44)=0,"",MAX(B44:Q44))</f>
-        <v>123.5</v>
+        <v>112</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="33" t="str">
         <f aca="false">IF(Übungen!$A7="","",Übungen!$A7)</f>
-        <v>Lunges</v>
-      </c>
-      <c r="B45" s="37" t="str">
+        <v>Adduktion</v>
+      </c>
+      <c r="B45" s="37" t="n">
         <f aca="false">IF($A45="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A45)*(Log!$B$4:$B$503=B$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A45)*(Log!$B$4:$B$503=B$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v/>
-      </c>
-      <c r="C45" s="37" t="str">
+        <v>238.916666666667</v>
+      </c>
+      <c r="C45" s="37" t="n">
         <f aca="false">IF($A45="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A45)*(Log!$B$4:$B$503=C$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A45)*(Log!$B$4:$B$503=C$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v/>
-      </c>
-      <c r="D45" s="37" t="str">
+        <v>254.166666666667</v>
+      </c>
+      <c r="D45" s="37" t="n">
         <f aca="false">IF($A45="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A45)*(Log!$B$4:$B$503=D$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A45)*(Log!$B$4:$B$503=D$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v/>
-      </c>
-      <c r="E45" s="37" t="str">
+        <v>264.333333333333</v>
+      </c>
+      <c r="E45" s="37" t="n">
         <f aca="false">IF($A45="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A45)*(Log!$B$4:$B$503=E$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A45)*(Log!$B$4:$B$503=E$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v/>
+        <v>279.583333333333</v>
       </c>
       <c r="F45" s="37" t="str">
         <f aca="false">IF($A45="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A45)*(Log!$B$4:$B$503=F$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A45)*(Log!$B$4:$B$503=F$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
@@ -21279,31 +21469,31 @@
         <f aca="false">IF($A45="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A45)*(Log!$B$4:$B$503=Q$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A45)*(Log!$B$4:$B$503=Q$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
         <v/>
       </c>
-      <c r="R45" s="36" t="str">
+      <c r="R45" s="36" t="n">
         <f aca="false">IF(COUNT(B45:Q45)=0,"",MAX(B45:Q45))</f>
-        <v/>
+        <v>279.583333333333</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="30" t="str">
         <f aca="false">IF(Übungen!$A8="","",Übungen!$A8)</f>
-        <v>Kickback</v>
-      </c>
-      <c r="B46" s="35" t="n">
+        <v>Rumänisches Kreuzheben</v>
+      </c>
+      <c r="B46" s="35" t="str">
         <f aca="false">IF($A46="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A46)*(Log!$B$4:$B$503=B$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A46)*(Log!$B$4:$B$503=B$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v>107.8</v>
-      </c>
-      <c r="C46" s="35" t="n">
+        <v/>
+      </c>
+      <c r="C46" s="35" t="str">
         <f aca="false">IF($A46="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A46)*(Log!$B$4:$B$503=C$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A46)*(Log!$B$4:$B$503=C$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v>102.666666666667</v>
-      </c>
-      <c r="D46" s="35" t="n">
+        <v/>
+      </c>
+      <c r="D46" s="35" t="str">
         <f aca="false">IF($A46="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A46)*(Log!$B$4:$B$503=D$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A46)*(Log!$B$4:$B$503=D$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v>117.6</v>
-      </c>
-      <c r="E46" s="35" t="n">
+        <v/>
+      </c>
+      <c r="E46" s="35" t="str">
         <f aca="false">IF($A46="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A46)*(Log!$B$4:$B$503=E$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A46)*(Log!$B$4:$B$503=E$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v>94.5</v>
+        <v/>
       </c>
       <c r="F46" s="35" t="str">
         <f aca="false">IF($A46="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A46)*(Log!$B$4:$B$503=F$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A46)*(Log!$B$4:$B$503=F$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
@@ -21353,31 +21543,31 @@
         <f aca="false">IF($A46="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A46)*(Log!$B$4:$B$503=Q$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A46)*(Log!$B$4:$B$503=Q$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
         <v/>
       </c>
-      <c r="R46" s="36" t="n">
+      <c r="R46" s="36" t="str">
         <f aca="false">IF(COUNT(B46:Q46)=0,"",MAX(B46:Q46))</f>
-        <v>117.6</v>
+        <v/>
       </c>
     </row>
     <row r="47" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="33" t="str">
         <f aca="false">IF(Übungen!$A9="","",Übungen!$A9)</f>
-        <v>Seitliche Kickbacks</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="B47" s="37" t="n">
         <f aca="false">IF($A47="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A47)*(Log!$B$4:$B$503=B$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A47)*(Log!$B$4:$B$503=B$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v>68.6</v>
+        <v>308</v>
       </c>
       <c r="C47" s="37" t="n">
         <f aca="false">IF($A47="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A47)*(Log!$B$4:$B$503=C$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A47)*(Log!$B$4:$B$503=C$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v>52.5</v>
-      </c>
-      <c r="D47" s="37" t="str">
+        <v>336</v>
+      </c>
+      <c r="D47" s="37" t="n">
         <f aca="false">IF($A47="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A47)*(Log!$B$4:$B$503=D$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A47)*(Log!$B$4:$B$503=D$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v/>
-      </c>
-      <c r="E47" s="37" t="str">
+        <v>360</v>
+      </c>
+      <c r="E47" s="37" t="n">
         <f aca="false">IF($A47="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A47)*(Log!$B$4:$B$503=E$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A47)*(Log!$B$4:$B$503=E$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v/>
+        <v>342</v>
       </c>
       <c r="F47" s="37" t="str">
         <f aca="false">IF($A47="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A47)*(Log!$B$4:$B$503=F$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A47)*(Log!$B$4:$B$503=F$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
@@ -21429,7 +21619,7 @@
       </c>
       <c r="R47" s="36" t="n">
         <f aca="false">IF(COUNT(B47:Q47)=0,"",MAX(B47:Q47))</f>
-        <v>68.6</v>
+        <v>360</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21509,23 +21699,23 @@
     <row r="49" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="33" t="str">
         <f aca="false">IF(Übungen!$A11="","",Übungen!$A11)</f>
-        <v>Hip Thrust</v>
+        <v>Seitliche Kickbacks</v>
       </c>
       <c r="B49" s="37" t="n">
         <f aca="false">IF($A49="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A49)*(Log!$B$4:$B$503=B$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A49)*(Log!$B$4:$B$503=B$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v>308</v>
+        <v>68.6</v>
       </c>
       <c r="C49" s="37" t="n">
         <f aca="false">IF($A49="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A49)*(Log!$B$4:$B$503=C$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A49)*(Log!$B$4:$B$503=C$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v>336</v>
-      </c>
-      <c r="D49" s="37" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="D49" s="37" t="str">
         <f aca="false">IF($A49="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A49)*(Log!$B$4:$B$503=D$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A49)*(Log!$B$4:$B$503=D$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v>360</v>
-      </c>
-      <c r="E49" s="37" t="n">
+        <v/>
+      </c>
+      <c r="E49" s="37" t="str">
         <f aca="false">IF($A49="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A49)*(Log!$B$4:$B$503=E$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A49)*(Log!$B$4:$B$503=E$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v>342</v>
+        <v/>
       </c>
       <c r="F49" s="37" t="str">
         <f aca="false">IF($A49="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A49)*(Log!$B$4:$B$503=F$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A49)*(Log!$B$4:$B$503=F$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
@@ -21577,7 +21767,7 @@
       </c>
       <c r="R49" s="36" t="n">
         <f aca="false">IF(COUNT(B49:Q49)=0,"",MAX(B49:Q49))</f>
-        <v>360</v>
+        <v>68.6</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21657,7 +21847,7 @@
     <row r="51" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="33" t="str">
         <f aca="false">IF(Übungen!$A13="","",Übungen!$A13)</f>
-        <v/>
+        <v>Lunges</v>
       </c>
       <c r="B51" s="37" t="str">
         <f aca="false">IF($A51="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A51)*(Log!$B$4:$B$503=B$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A51)*(Log!$B$4:$B$503=B$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
@@ -21731,23 +21921,23 @@
     <row r="52" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="30" t="str">
         <f aca="false">IF(Übungen!$A14="","",Übungen!$A14)</f>
-        <v/>
-      </c>
-      <c r="B52" s="35" t="str">
+        <v>Kickback</v>
+      </c>
+      <c r="B52" s="35" t="n">
         <f aca="false">IF($A52="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A52)*(Log!$B$4:$B$503=B$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A52)*(Log!$B$4:$B$503=B$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v/>
-      </c>
-      <c r="C52" s="35" t="str">
+        <v>107.8</v>
+      </c>
+      <c r="C52" s="35" t="n">
         <f aca="false">IF($A52="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A52)*(Log!$B$4:$B$503=C$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A52)*(Log!$B$4:$B$503=C$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v/>
-      </c>
-      <c r="D52" s="35" t="str">
+        <v>102.666666666667</v>
+      </c>
+      <c r="D52" s="35" t="n">
         <f aca="false">IF($A52="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A52)*(Log!$B$4:$B$503=D$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A52)*(Log!$B$4:$B$503=D$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v/>
-      </c>
-      <c r="E52" s="35" t="str">
+        <v>117.6</v>
+      </c>
+      <c r="E52" s="35" t="n">
         <f aca="false">IF($A52="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A52)*(Log!$B$4:$B$503=E$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A52)*(Log!$B$4:$B$503=E$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v/>
+        <v>94.5</v>
       </c>
       <c r="F52" s="35" t="str">
         <f aca="false">IF($A52="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A52)*(Log!$B$4:$B$503=F$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A52)*(Log!$B$4:$B$503=F$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
@@ -21797,9 +21987,9 @@
         <f aca="false">IF($A52="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A52)*(Log!$B$4:$B$503=Q$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A52)*(Log!$B$4:$B$503=Q$41)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
         <v/>
       </c>
-      <c r="R52" s="36" t="str">
+      <c r="R52" s="36" t="n">
         <f aca="false">IF(COUNT(B52:Q52)=0,"",MAX(B52:Q52))</f>
-        <v/>
+        <v>117.6</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22032,17 +22222,12 @@
     <mergeCell ref="A22:R22"/>
     <mergeCell ref="A40:R40"/>
   </mergeCells>
-  <conditionalFormatting sqref="B6:Q19">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF9EC5E8"/>
-      </colorScale>
+  <conditionalFormatting sqref="A6:A19">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>Übungen!$I4="nein"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B24:Q37">
+  <conditionalFormatting sqref="B6:Q19">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22052,8 +22237,28 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A24:A37">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>Übungen!$I4="nein"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24:Q37">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF9EC5E8"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A42:A55">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>Übungen!$I4="nein"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B42:Q55">
-    <cfRule type="colorScale" priority="4">
+    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="max" val="0"/>
@@ -22094,7 +22299,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -22109,7 +22314,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -22124,89 +22329,89 @@
     </row>
     <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="J3" s="16" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="K3" s="16" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="30" t="str">
         <f aca="false">IF(Übungen!$A4="","",Übungen!$A4)</f>
-        <v>Adduktion</v>
-      </c>
-      <c r="B4" s="31" t="n">
+        <v>Hackenschmidt-Kniebeuge</v>
+      </c>
+      <c r="B4" s="31" t="str">
         <f aca="false">IF($A4="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A4)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))=0,"",SUMPRODUCT(MIN((Log!$D$4:$D$503=$A4)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503+((Log!$D$4:$D$503&lt;&gt;$A4)+(Log!$E$4:$E$503&lt;&gt;"A")&gt;0)*9999))))</f>
-        <v>1</v>
-      </c>
-      <c r="C4" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C4" s="31" t="str">
         <f aca="false">IF($B4="","",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A4,Log!$B$4:$B$503,$B4,Log!$E$4:$E$503,"A"))</f>
-        <v>4117.5</v>
-      </c>
-      <c r="D4" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D4" s="31" t="str">
         <f aca="false">IF($A4="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A4)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A4)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))))</f>
-        <v>4</v>
-      </c>
-      <c r="E4" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E4" s="31" t="str">
         <f aca="false">IF($D4="","",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A4,Log!$B$4:$B$503,$D4,Log!$E$4:$E$503,"A"))</f>
-        <v>6862.5</v>
-      </c>
-      <c r="F4" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F4" s="31" t="str">
         <f aca="false">IF(OR($C4="",$E4=""),"",$E4-$C4)</f>
-        <v>2745</v>
-      </c>
-      <c r="G4" s="38" t="n">
+        <v/>
+      </c>
+      <c r="G4" s="38" t="str">
         <f aca="false">IF(OR($C4="",$E4="",$C4=0),"",$E4/$C4-1)</f>
-        <v>0.666666666666667</v>
-      </c>
-      <c r="H4" s="35" t="n">
+        <v/>
+      </c>
+      <c r="H4" s="35" t="str">
         <f aca="false">IF($D4="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A4)*(Log!$B$4:$B$503=$D4)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A4)*(Log!$B$4:$B$503=$D4)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>152.5</v>
-      </c>
-      <c r="I4" s="35" t="n">
+        <v/>
+      </c>
+      <c r="I4" s="35" t="str">
         <f aca="false">IF($A4="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A4)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A4)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>152.5</v>
-      </c>
-      <c r="J4" s="35" t="n">
+        <v/>
+      </c>
+      <c r="J4" s="35" t="str">
         <f aca="false">IF(OR($H4="",$I4=""),"",$H4-$I4)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="K4" s="39" t="str">
         <f aca="false">IF($G4="","",IF($G4&gt;0.05,"steigend",IF($G4&lt;-0.05,"fallend","stabil")))</f>
-        <v>steigend</v>
+        <v/>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="str">
         <f aca="false">IF(Übungen!$A5="","",Übungen!$A5)</f>
-        <v>Beinstrecker</v>
+        <v>Split Squat</v>
       </c>
       <c r="B5" s="34" t="n">
         <f aca="false">IF($A5="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A5)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))=0,"",SUMPRODUCT(MIN((Log!$D$4:$D$503=$A5)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503+((Log!$D$4:$D$503&lt;&gt;$A5)+(Log!$E$4:$E$503&lt;&gt;"A")&gt;0)*9999))))</f>
@@ -22214,7 +22419,7 @@
       </c>
       <c r="C5" s="34" t="n">
         <f aca="false">IF($B5="","",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A5,Log!$B$4:$B$503,$B5,Log!$E$4:$E$503,"A"))</f>
-        <v>1205</v>
+        <v>1610</v>
       </c>
       <c r="D5" s="34" t="n">
         <f aca="false">IF($A5="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A5)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A5)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))))</f>
@@ -22222,15 +22427,15 @@
       </c>
       <c r="E5" s="34" t="n">
         <f aca="false">IF($D5="","",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A5,Log!$B$4:$B$503,$D5,Log!$E$4:$E$503,"A"))</f>
-        <v>1600</v>
+        <v>1640</v>
       </c>
       <c r="F5" s="34" t="n">
         <f aca="false">IF(OR($C5="",$E5=""),"",$E5-$C5)</f>
-        <v>395</v>
+        <v>30</v>
       </c>
       <c r="G5" s="40" t="n">
         <f aca="false">IF(OR($C5="",$E5="",$C5=0),"",$E5/$C5-1)</f>
-        <v>0.327800829875519</v>
+        <v>0.0186335403726707</v>
       </c>
       <c r="H5" s="37" t="n">
         <f aca="false">IF($D5="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A5)*(Log!$B$4:$B$503=$D5)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A5)*(Log!$B$4:$B$503=$D5)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
@@ -22238,21 +22443,21 @@
       </c>
       <c r="I5" s="37" t="n">
         <f aca="false">IF($A5="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A5)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A5)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="J5" s="37" t="n">
         <f aca="false">IF(OR($H5="",$I5=""),"",$H5-$I5)</f>
-        <v>-5</v>
+        <v>-25</v>
       </c>
       <c r="K5" s="41" t="str">
         <f aca="false">IF($G5="","",IF($G5&gt;0.05,"steigend",IF($G5&lt;-0.05,"fallend","stabil")))</f>
-        <v>steigend</v>
+        <v>stabil</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="str">
         <f aca="false">IF(Übungen!$A6="","",Übungen!$A6)</f>
-        <v>Split Squat</v>
+        <v>Beinstrecker</v>
       </c>
       <c r="B6" s="31" t="n">
         <f aca="false">IF($A6="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A6)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))=0,"",SUMPRODUCT(MIN((Log!$D$4:$D$503=$A6)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503+((Log!$D$4:$D$503&lt;&gt;$A6)+(Log!$E$4:$E$503&lt;&gt;"A")&gt;0)*9999))))</f>
@@ -22260,7 +22465,7 @@
       </c>
       <c r="C6" s="31" t="n">
         <f aca="false">IF($B6="","",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A6,Log!$B$4:$B$503,$B6,Log!$E$4:$E$503,"A"))</f>
-        <v>1610</v>
+        <v>1205</v>
       </c>
       <c r="D6" s="31" t="n">
         <f aca="false">IF($A6="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A6)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A6)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))))</f>
@@ -22268,15 +22473,15 @@
       </c>
       <c r="E6" s="31" t="n">
         <f aca="false">IF($D6="","",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A6,Log!$B$4:$B$503,$D6,Log!$E$4:$E$503,"A"))</f>
-        <v>1640</v>
+        <v>1600</v>
       </c>
       <c r="F6" s="31" t="n">
         <f aca="false">IF(OR($C6="",$E6=""),"",$E6-$C6)</f>
-        <v>30</v>
+        <v>395</v>
       </c>
       <c r="G6" s="38" t="n">
         <f aca="false">IF(OR($C6="",$E6="",$C6=0),"",$E6/$C6-1)</f>
-        <v>0.0186335403726707</v>
+        <v>0.327800829875519</v>
       </c>
       <c r="H6" s="35" t="n">
         <f aca="false">IF($D6="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A6)*(Log!$B$4:$B$503=$D6)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A6)*(Log!$B$4:$B$503=$D6)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
@@ -22284,21 +22489,21 @@
       </c>
       <c r="I6" s="35" t="n">
         <f aca="false">IF($A6="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A6)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A6)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="J6" s="35" t="n">
         <f aca="false">IF(OR($H6="",$I6=""),"",$H6-$I6)</f>
-        <v>-25</v>
+        <v>-5</v>
       </c>
       <c r="K6" s="39" t="str">
         <f aca="false">IF($G6="","",IF($G6&gt;0.05,"steigend",IF($G6&lt;-0.05,"fallend","stabil")))</f>
-        <v>stabil</v>
+        <v>steigend</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="str">
         <f aca="false">IF(Übungen!$A7="","",Übungen!$A7)</f>
-        <v>Lunges</v>
+        <v>Adduktion</v>
       </c>
       <c r="B7" s="34" t="n">
         <f aca="false">IF($A7="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A7)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))=0,"",SUMPRODUCT(MIN((Log!$D$4:$D$503=$A7)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503+((Log!$D$4:$D$503&lt;&gt;$A7)+(Log!$E$4:$E$503&lt;&gt;"A")&gt;0)*9999))))</f>
@@ -22306,31 +22511,31 @@
       </c>
       <c r="C7" s="34" t="n">
         <f aca="false">IF($B7="","",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A7,Log!$B$4:$B$503,$B7,Log!$E$4:$E$503,"A"))</f>
-        <v>0</v>
+        <v>4117.5</v>
       </c>
       <c r="D7" s="34" t="n">
         <f aca="false">IF($A7="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A7)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A7)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" s="34" t="n">
         <f aca="false">IF($D7="","",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A7,Log!$B$4:$B$503,$D7,Log!$E$4:$E$503,"A"))</f>
-        <v>0</v>
+        <v>6862.5</v>
       </c>
       <c r="F7" s="34" t="n">
         <f aca="false">IF(OR($C7="",$E7=""),"",$E7-$C7)</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="40" t="str">
+        <v>2745</v>
+      </c>
+      <c r="G7" s="40" t="n">
         <f aca="false">IF(OR($C7="",$E7="",$C7=0),"",$E7/$C7-1)</f>
-        <v/>
+        <v>0.666666666666667</v>
       </c>
       <c r="H7" s="37" t="n">
         <f aca="false">IF($D7="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A7)*(Log!$B$4:$B$503=$D7)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A7)*(Log!$B$4:$B$503=$D7)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>18</v>
+        <v>152.5</v>
       </c>
       <c r="I7" s="37" t="n">
         <f aca="false">IF($A7="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A7)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A7)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>18</v>
+        <v>152.5</v>
       </c>
       <c r="J7" s="37" t="n">
         <f aca="false">IF(OR($H7="",$I7=""),"",$H7-$I7)</f>
@@ -22338,59 +22543,59 @@
       </c>
       <c r="K7" s="41" t="str">
         <f aca="false">IF($G7="","",IF($G7&gt;0.05,"steigend",IF($G7&lt;-0.05,"fallend","stabil")))</f>
-        <v/>
+        <v>steigend</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="str">
         <f aca="false">IF(Übungen!$A8="","",Übungen!$A8)</f>
-        <v>Kickback</v>
-      </c>
-      <c r="B8" s="31" t="n">
+        <v>Rumänisches Kreuzheben</v>
+      </c>
+      <c r="B8" s="31" t="str">
         <f aca="false">IF($A8="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A8)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))=0,"",SUMPRODUCT(MIN((Log!$D$4:$D$503=$A8)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503+((Log!$D$4:$D$503&lt;&gt;$A8)+(Log!$E$4:$E$503&lt;&gt;"A")&gt;0)*9999))))</f>
-        <v>1</v>
-      </c>
-      <c r="C8" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C8" s="31" t="str">
         <f aca="false">IF($B8="","",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A8,Log!$B$4:$B$503,$B8,Log!$E$4:$E$503,"A"))</f>
-        <v>1974</v>
-      </c>
-      <c r="D8" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D8" s="31" t="str">
         <f aca="false">IF($A8="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A8)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A8)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))))</f>
-        <v>4</v>
-      </c>
-      <c r="E8" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E8" s="31" t="str">
         <f aca="false">IF($D8="","",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A8,Log!$B$4:$B$503,$D8,Log!$E$4:$E$503,"A"))</f>
-        <v>1785</v>
-      </c>
-      <c r="F8" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F8" s="31" t="str">
         <f aca="false">IF(OR($C8="",$E8=""),"",$E8-$C8)</f>
-        <v>-189</v>
-      </c>
-      <c r="G8" s="38" t="n">
+        <v/>
+      </c>
+      <c r="G8" s="38" t="str">
         <f aca="false">IF(OR($C8="",$E8="",$C8=0),"",$E8/$C8-1)</f>
-        <v>-0.0957446808510638</v>
-      </c>
-      <c r="H8" s="35" t="n">
+        <v/>
+      </c>
+      <c r="H8" s="35" t="str">
         <f aca="false">IF($D8="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A8)*(Log!$B$4:$B$503=$D8)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A8)*(Log!$B$4:$B$503=$D8)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>63</v>
-      </c>
-      <c r="I8" s="35" t="n">
+        <v/>
+      </c>
+      <c r="I8" s="35" t="str">
         <f aca="false">IF($A8="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A8)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A8)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>84</v>
-      </c>
-      <c r="J8" s="35" t="n">
+        <v/>
+      </c>
+      <c r="J8" s="35" t="str">
         <f aca="false">IF(OR($H8="",$I8=""),"",$H8-$I8)</f>
-        <v>-21</v>
+        <v/>
       </c>
       <c r="K8" s="39" t="str">
         <f aca="false">IF($G8="","",IF($G8&gt;0.05,"steigend",IF($G8&lt;-0.05,"fallend","stabil")))</f>
-        <v>fallend</v>
+        <v/>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="str">
         <f aca="false">IF(Übungen!$A9="","",Übungen!$A9)</f>
-        <v>Seitliche Kickbacks</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="B9" s="34" t="n">
         <f aca="false">IF($A9="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A9)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))=0,"",SUMPRODUCT(MIN((Log!$D$4:$D$503=$A9)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503+((Log!$D$4:$D$503&lt;&gt;$A9)+(Log!$E$4:$E$503&lt;&gt;"A")&gt;0)*9999))))</f>
@@ -22398,39 +22603,39 @@
       </c>
       <c r="C9" s="34" t="n">
         <f aca="false">IF($B9="","",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A9,Log!$B$4:$B$503,$B9,Log!$E$4:$E$503,"A"))</f>
-        <v>1078</v>
+        <v>4560</v>
       </c>
       <c r="D9" s="34" t="n">
         <f aca="false">IF($A9="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A9)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A9)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E9" s="34" t="n">
         <f aca="false">IF($D9="","",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A9,Log!$B$4:$B$503,$D9,Log!$E$4:$E$503,"A"))</f>
-        <v>975</v>
+        <v>6480</v>
       </c>
       <c r="F9" s="34" t="n">
         <f aca="false">IF(OR($C9="",$E9=""),"",$E9-$C9)</f>
-        <v>-103</v>
+        <v>1920</v>
       </c>
       <c r="G9" s="40" t="n">
         <f aca="false">IF(OR($C9="",$E9="",$C9=0),"",$E9/$C9-1)</f>
-        <v>-0.0955473098330241</v>
+        <v>0.421052631578947</v>
       </c>
       <c r="H9" s="37" t="n">
         <f aca="false">IF($D9="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A9)*(Log!$B$4:$B$503=$D9)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A9)*(Log!$B$4:$B$503=$D9)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>35</v>
+        <v>270</v>
       </c>
       <c r="I9" s="37" t="n">
         <f aca="false">IF($A9="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A9)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A9)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>49</v>
+        <v>280</v>
       </c>
       <c r="J9" s="37" t="n">
         <f aca="false">IF(OR($H9="",$I9=""),"",$H9-$I9)</f>
-        <v>-14</v>
+        <v>-10</v>
       </c>
       <c r="K9" s="41" t="str">
         <f aca="false">IF($G9="","",IF($G9&gt;0.05,"steigend",IF($G9&lt;-0.05,"fallend","stabil")))</f>
-        <v>fallend</v>
+        <v>steigend</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22482,7 +22687,7 @@
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="str">
         <f aca="false">IF(Übungen!$A11="","",Übungen!$A11)</f>
-        <v>Hip Thrust</v>
+        <v>Seitliche Kickbacks</v>
       </c>
       <c r="B11" s="34" t="n">
         <f aca="false">IF($A11="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A11)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))=0,"",SUMPRODUCT(MIN((Log!$D$4:$D$503=$A11)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503+((Log!$D$4:$D$503&lt;&gt;$A11)+(Log!$E$4:$E$503&lt;&gt;"A")&gt;0)*9999))))</f>
@@ -22490,39 +22695,39 @@
       </c>
       <c r="C11" s="34" t="n">
         <f aca="false">IF($B11="","",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A11,Log!$B$4:$B$503,$B11,Log!$E$4:$E$503,"A"))</f>
-        <v>4560</v>
+        <v>1078</v>
       </c>
       <c r="D11" s="34" t="n">
         <f aca="false">IF($A11="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A11)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A11)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))))</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E11" s="34" t="n">
         <f aca="false">IF($D11="","",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A11,Log!$B$4:$B$503,$D11,Log!$E$4:$E$503,"A"))</f>
-        <v>6480</v>
+        <v>975</v>
       </c>
       <c r="F11" s="34" t="n">
         <f aca="false">IF(OR($C11="",$E11=""),"",$E11-$C11)</f>
-        <v>1920</v>
+        <v>-103</v>
       </c>
       <c r="G11" s="40" t="n">
         <f aca="false">IF(OR($C11="",$E11="",$C11=0),"",$E11/$C11-1)</f>
-        <v>0.421052631578947</v>
+        <v>-0.0955473098330241</v>
       </c>
       <c r="H11" s="37" t="n">
         <f aca="false">IF($D11="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A11)*(Log!$B$4:$B$503=$D11)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A11)*(Log!$B$4:$B$503=$D11)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>270</v>
+        <v>35</v>
       </c>
       <c r="I11" s="37" t="n">
         <f aca="false">IF($A11="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A11)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A11)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>280</v>
+        <v>49</v>
       </c>
       <c r="J11" s="37" t="n">
         <f aca="false">IF(OR($H11="",$I11=""),"",$H11-$I11)</f>
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="K11" s="41" t="str">
         <f aca="false">IF($G11="","",IF($G11&gt;0.05,"steigend",IF($G11&lt;-0.05,"fallend","stabil")))</f>
-        <v>steigend</v>
+        <v>fallend</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22574,43 +22779,43 @@
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="str">
         <f aca="false">IF(Übungen!$A13="","",Übungen!$A13)</f>
-        <v/>
-      </c>
-      <c r="B13" s="34" t="str">
+        <v>Lunges</v>
+      </c>
+      <c r="B13" s="34" t="n">
         <f aca="false">IF($A13="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A13)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))=0,"",SUMPRODUCT(MIN((Log!$D$4:$D$503=$A13)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503+((Log!$D$4:$D$503&lt;&gt;$A13)+(Log!$E$4:$E$503&lt;&gt;"A")&gt;0)*9999))))</f>
-        <v/>
-      </c>
-      <c r="C13" s="34" t="str">
+        <v>1</v>
+      </c>
+      <c r="C13" s="34" t="n">
         <f aca="false">IF($B13="","",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A13,Log!$B$4:$B$503,$B13,Log!$E$4:$E$503,"A"))</f>
-        <v/>
-      </c>
-      <c r="D13" s="34" t="str">
+        <v>0</v>
+      </c>
+      <c r="D13" s="34" t="n">
         <f aca="false">IF($A13="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A13)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A13)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))))</f>
-        <v/>
-      </c>
-      <c r="E13" s="34" t="str">
+        <v>3</v>
+      </c>
+      <c r="E13" s="34" t="n">
         <f aca="false">IF($D13="","",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A13,Log!$B$4:$B$503,$D13,Log!$E$4:$E$503,"A"))</f>
-        <v/>
-      </c>
-      <c r="F13" s="34" t="str">
+        <v>0</v>
+      </c>
+      <c r="F13" s="34" t="n">
         <f aca="false">IF(OR($C13="",$E13=""),"",$E13-$C13)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G13" s="40" t="str">
         <f aca="false">IF(OR($C13="",$E13="",$C13=0),"",$E13/$C13-1)</f>
         <v/>
       </c>
-      <c r="H13" s="37" t="str">
+      <c r="H13" s="37" t="n">
         <f aca="false">IF($D13="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A13)*(Log!$B$4:$B$503=$D13)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A13)*(Log!$B$4:$B$503=$D13)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v/>
-      </c>
-      <c r="I13" s="37" t="str">
+        <v>18</v>
+      </c>
+      <c r="I13" s="37" t="n">
         <f aca="false">IF($A13="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A13)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A13)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v/>
-      </c>
-      <c r="J13" s="37" t="str">
+        <v>18</v>
+      </c>
+      <c r="J13" s="37" t="n">
         <f aca="false">IF(OR($H13="",$I13=""),"",$H13-$I13)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K13" s="41" t="str">
         <f aca="false">IF($G13="","",IF($G13&gt;0.05,"steigend",IF($G13&lt;-0.05,"fallend","stabil")))</f>
@@ -22620,47 +22825,47 @@
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="30" t="str">
         <f aca="false">IF(Übungen!$A14="","",Übungen!$A14)</f>
-        <v/>
-      </c>
-      <c r="B14" s="31" t="str">
+        <v>Kickback</v>
+      </c>
+      <c r="B14" s="31" t="n">
         <f aca="false">IF($A14="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A14)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))=0,"",SUMPRODUCT(MIN((Log!$D$4:$D$503=$A14)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503+((Log!$D$4:$D$503&lt;&gt;$A14)+(Log!$E$4:$E$503&lt;&gt;"A")&gt;0)*9999))))</f>
-        <v/>
-      </c>
-      <c r="C14" s="31" t="str">
+        <v>1</v>
+      </c>
+      <c r="C14" s="31" t="n">
         <f aca="false">IF($B14="","",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A14,Log!$B$4:$B$503,$B14,Log!$E$4:$E$503,"A"))</f>
-        <v/>
-      </c>
-      <c r="D14" s="31" t="str">
+        <v>1974</v>
+      </c>
+      <c r="D14" s="31" t="n">
         <f aca="false">IF($A14="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A14)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A14)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))))</f>
-        <v/>
-      </c>
-      <c r="E14" s="31" t="str">
+        <v>4</v>
+      </c>
+      <c r="E14" s="31" t="n">
         <f aca="false">IF($D14="","",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A14,Log!$B$4:$B$503,$D14,Log!$E$4:$E$503,"A"))</f>
-        <v/>
-      </c>
-      <c r="F14" s="31" t="str">
+        <v>1785</v>
+      </c>
+      <c r="F14" s="31" t="n">
         <f aca="false">IF(OR($C14="",$E14=""),"",$E14-$C14)</f>
-        <v/>
-      </c>
-      <c r="G14" s="38" t="str">
+        <v>-189</v>
+      </c>
+      <c r="G14" s="38" t="n">
         <f aca="false">IF(OR($C14="",$E14="",$C14=0),"",$E14/$C14-1)</f>
-        <v/>
-      </c>
-      <c r="H14" s="35" t="str">
+        <v>-0.0957446808510638</v>
+      </c>
+      <c r="H14" s="35" t="n">
         <f aca="false">IF($D14="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A14)*(Log!$B$4:$B$503=$D14)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A14)*(Log!$B$4:$B$503=$D14)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v/>
-      </c>
-      <c r="I14" s="35" t="str">
+        <v>63</v>
+      </c>
+      <c r="I14" s="35" t="n">
         <f aca="false">IF($A14="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A14)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A14)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v/>
-      </c>
-      <c r="J14" s="35" t="str">
+        <v>84</v>
+      </c>
+      <c r="J14" s="35" t="n">
         <f aca="false">IF(OR($H14="",$I14=""),"",$H14-$I14)</f>
-        <v/>
+        <v>-21</v>
       </c>
       <c r="K14" s="39" t="str">
         <f aca="false">IF($G14="","",IF($G14&gt;0.05,"steigend",IF($G14&lt;-0.05,"fallend","stabil")))</f>
-        <v/>
+        <v>fallend</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22803,7 +23008,7 @@
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="42" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B19" s="42"/>
       <c r="C19" s="42"/>
@@ -22823,19 +23028,24 @@
     <mergeCell ref="A19:K19"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:G17">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>AND($G4&lt;&gt;"",$G4&gt;0.05)</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>AND($G4&lt;&gt;"",$G4&lt;-0.05)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4:K17">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>$K4="steigend"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>$K4="fallend"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4:K17">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>Übungen!$I4="nein"</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
@@ -22874,7 +23084,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -22892,7 +23102,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -22910,110 +23120,110 @@
     </row>
     <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="J3" s="16" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="K3" s="16" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="L3" s="16" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="M3" s="16" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="N3" s="16" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="30" t="str">
         <f aca="false">IF(Übungen!$A4="","",Übungen!$A4)</f>
-        <v>Adduktion</v>
+        <v>Hackenschmidt-Kniebeuge</v>
       </c>
       <c r="B4" s="43" t="str">
         <f aca="false">IF(Übungen!$B4="","",Übungen!$B4)</f>
         <v>Beine vorne</v>
       </c>
-      <c r="C4" s="31" t="n">
+      <c r="C4" s="31" t="str">
         <f aca="false">IF($D4="","",SUMPRODUCT((COUNTIFS(Log!$D$4:$D$503,$A4,Log!$E$4:$E$503,"A",Log!$B$4:$B$503,Einheiten!$A$4:$A$27)&gt;0)*1))</f>
-        <v>4</v>
-      </c>
-      <c r="D4" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D4" s="31" t="str">
         <f aca="false">IF($A4="","",IF(COUNTIFS(Log!$D$4:$D$503,$A4,Log!$E$4:$E$503,"A")=0,"",COUNTIFS(Log!$D$4:$D$503,$A4,Log!$E$4:$E$503,"A")))</f>
-        <v>8</v>
-      </c>
-      <c r="E4" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E4" s="31" t="str">
         <f aca="false">IF($D4="","",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A4,Log!$E$4:$E$503,"A"))</f>
-        <v>21807.5</v>
-      </c>
-      <c r="F4" s="44" t="n">
+        <v/>
+      </c>
+      <c r="F4" s="44" t="str">
         <f aca="false">IF($D4="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A4)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A4)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>152.5</v>
-      </c>
-      <c r="G4" s="31" t="n">
+        <v/>
+      </c>
+      <c r="G4" s="31" t="str">
         <f aca="false">IF($F4="","",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A4)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503=$F4)*Log!$B$4:$B$503)))</f>
-        <v>4</v>
-      </c>
-      <c r="H4" s="44" t="n">
+        <v/>
+      </c>
+      <c r="H4" s="44" t="str">
         <f aca="false">IF($D4="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A4)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A4)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v>279.583333333333</v>
-      </c>
-      <c r="I4" s="31" t="n">
+        <v/>
+      </c>
+      <c r="I4" s="31" t="str">
         <f aca="false">IF($H4="","",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A4)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*(ROUND(Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30),6)=ROUND($H4,6))*Log!$B$4:$B$503)))</f>
-        <v>4</v>
-      </c>
-      <c r="J4" s="31" t="n">
+        <v/>
+      </c>
+      <c r="J4" s="31" t="str">
         <f aca="false">IF($D4="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A4)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*Log!$G$4:$G$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A4)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*Log!$G$4:$G$503))))</f>
-        <v>3812.5</v>
-      </c>
-      <c r="K4" s="31" t="n">
+        <v/>
+      </c>
+      <c r="K4" s="31" t="str">
         <f aca="false">IF($D4="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A4)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A4)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))))</f>
-        <v>4</v>
-      </c>
-      <c r="L4" s="35" t="n">
+        <v/>
+      </c>
+      <c r="L4" s="35" t="str">
         <f aca="false">IF($K4="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A4)*(Log!$B$4:$B$503=$K4)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A4)*(Log!$B$4:$B$503=$K4)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>152.5</v>
-      </c>
-      <c r="M4" s="31" t="n">
+        <v/>
+      </c>
+      <c r="M4" s="31" t="str">
         <f aca="false">IF($L4="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A4)*(Log!$B$4:$B$503=$K4)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503=$L4)*Log!$G$4:$G$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A4)*(Log!$B$4:$B$503=$K4)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503=$L4)*Log!$G$4:$G$503))))</f>
-        <v>25</v>
-      </c>
-      <c r="N4" s="44" t="n">
-        <f aca="false">IF($L4="","",ROUND($L4*1.025*2,0)/2)</f>
-        <v>156.5</v>
+        <v/>
+      </c>
+      <c r="N4" s="44" t="str">
+        <f aca="false">IF($L4&lt;&gt;"",IF(Übungen!$H4="",ROUND($L4*1.025*2,0)/2,MIN(ROUND($L4*1.025*2,0)/2,Übungen!$H4)),IF(Übungen!$G4="","",Übungen!$G4))</f>
+        <v/>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="str">
         <f aca="false">IF(Übungen!$A5="","",Übungen!$A5)</f>
-        <v>Beinstrecker</v>
+        <v>Split Squat</v>
       </c>
       <c r="B5" s="4" t="str">
         <f aca="false">IF(Übungen!$B5="","",Übungen!$B5)</f>
@@ -23025,31 +23235,31 @@
       </c>
       <c r="D5" s="34" t="n">
         <f aca="false">IF($A5="","",IF(COUNTIFS(Log!$D$4:$D$503,$A5,Log!$E$4:$E$503,"A")=0,"",COUNTIFS(Log!$D$4:$D$503,$A5,Log!$E$4:$E$503,"A")))</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E5" s="34" t="n">
         <f aca="false">IF($D5="","",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A5,Log!$E$4:$E$503,"A"))</f>
-        <v>5865</v>
+        <v>7100</v>
       </c>
       <c r="F5" s="45" t="n">
         <f aca="false">IF($D5="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A5)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A5)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="G5" s="34" t="n">
         <f aca="false">IF($F5="","",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A5)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503=$F5)*Log!$B$4:$B$503)))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" s="45" t="n">
         <f aca="false">IF($D5="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A5)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A5)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v>112</v>
+        <v>123.5</v>
       </c>
       <c r="I5" s="34" t="n">
         <f aca="false">IF($H5="","",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A5)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*(ROUND(Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30),6)=ROUND($H5,6))*Log!$B$4:$B$503)))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J5" s="34" t="n">
         <f aca="false">IF($D5="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A5)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*Log!$G$4:$G$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A5)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*Log!$G$4:$G$503))))</f>
-        <v>960</v>
+        <v>855</v>
       </c>
       <c r="K5" s="34" t="n">
         <f aca="false">IF($D5="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A5)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A5)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))))</f>
@@ -23061,17 +23271,17 @@
       </c>
       <c r="M5" s="34" t="n">
         <f aca="false">IF($L5="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A5)*(Log!$B$4:$B$503=$K5)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503=$L5)*Log!$G$4:$G$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A5)*(Log!$B$4:$B$503=$K5)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503=$L5)*Log!$G$4:$G$503))))</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N5" s="45" t="n">
-        <f aca="false">IF($L5="","",ROUND($L5*1.025*2,0)/2)</f>
+        <f aca="false">IF($L5&lt;&gt;"",IF(Übungen!$H5="",ROUND($L5*1.025*2,0)/2,MIN(ROUND($L5*1.025*2,0)/2,Übungen!$H5)),IF(Übungen!$G5="","",Übungen!$G5))</f>
         <v>82</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="str">
         <f aca="false">IF(Übungen!$A6="","",Übungen!$A6)</f>
-        <v>Split Squat</v>
+        <v>Beinstrecker</v>
       </c>
       <c r="B6" s="43" t="str">
         <f aca="false">IF(Übungen!$B6="","",Übungen!$B6)</f>
@@ -23083,31 +23293,31 @@
       </c>
       <c r="D6" s="31" t="n">
         <f aca="false">IF($A6="","",IF(COUNTIFS(Log!$D$4:$D$503,$A6,Log!$E$4:$E$503,"A")=0,"",COUNTIFS(Log!$D$4:$D$503,$A6,Log!$E$4:$E$503,"A")))</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E6" s="31" t="n">
         <f aca="false">IF($D6="","",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A6,Log!$E$4:$E$503,"A"))</f>
-        <v>7100</v>
+        <v>5865</v>
       </c>
       <c r="F6" s="44" t="n">
         <f aca="false">IF($D6="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A6)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A6)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="G6" s="31" t="n">
         <f aca="false">IF($F6="","",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A6)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503=$F6)*Log!$B$4:$B$503)))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" s="44" t="n">
         <f aca="false">IF($D6="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A6)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A6)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v>123.5</v>
+        <v>112</v>
       </c>
       <c r="I6" s="31" t="n">
         <f aca="false">IF($H6="","",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A6)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*(ROUND(Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30),6)=ROUND($H6,6))*Log!$B$4:$B$503)))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6" s="31" t="n">
         <f aca="false">IF($D6="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A6)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*Log!$G$4:$G$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A6)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*Log!$G$4:$G$503))))</f>
-        <v>855</v>
+        <v>960</v>
       </c>
       <c r="K6" s="31" t="n">
         <f aca="false">IF($D6="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A6)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A6)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))))</f>
@@ -23119,17 +23329,17 @@
       </c>
       <c r="M6" s="31" t="n">
         <f aca="false">IF($L6="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A6)*(Log!$B$4:$B$503=$K6)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503=$L6)*Log!$G$4:$G$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A6)*(Log!$B$4:$B$503=$K6)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503=$L6)*Log!$G$4:$G$503))))</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N6" s="44" t="n">
-        <f aca="false">IF($L6="","",ROUND($L6*1.025*2,0)/2)</f>
+        <f aca="false">IF($L6&lt;&gt;"",IF(Übungen!$H6="",ROUND($L6*1.025*2,0)/2,MIN(ROUND($L6*1.025*2,0)/2,Übungen!$H6)),IF(Übungen!$G6="","",Übungen!$G6))</f>
         <v>82</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="str">
         <f aca="false">IF(Übungen!$A7="","",Übungen!$A7)</f>
-        <v>Lunges</v>
+        <v>Adduktion</v>
       </c>
       <c r="B7" s="4" t="str">
         <f aca="false">IF(Übungen!$B7="","",Übungen!$B7)</f>
@@ -23137,115 +23347,115 @@
       </c>
       <c r="C7" s="34" t="n">
         <f aca="false">IF($D7="","",SUMPRODUCT((COUNTIFS(Log!$D$4:$D$503,$A7,Log!$E$4:$E$503,"A",Log!$B$4:$B$503,Einheiten!$A$4:$A$27)&gt;0)*1))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" s="34" t="n">
         <f aca="false">IF($A7="","",IF(COUNTIFS(Log!$D$4:$D$503,$A7,Log!$E$4:$E$503,"A")=0,"",COUNTIFS(Log!$D$4:$D$503,$A7,Log!$E$4:$E$503,"A")))</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E7" s="34" t="n">
         <f aca="false">IF($D7="","",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A7,Log!$E$4:$E$503,"A"))</f>
-        <v>0</v>
+        <v>21807.5</v>
       </c>
       <c r="F7" s="45" t="n">
         <f aca="false">IF($D7="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A7)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A7)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>18</v>
+        <v>152.5</v>
       </c>
       <c r="G7" s="34" t="n">
         <f aca="false">IF($F7="","",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A7)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503=$F7)*Log!$B$4:$B$503)))</f>
-        <v>3</v>
-      </c>
-      <c r="H7" s="45" t="str">
+        <v>4</v>
+      </c>
+      <c r="H7" s="45" t="n">
         <f aca="false">IF($D7="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A7)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A7)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v/>
-      </c>
-      <c r="I7" s="34" t="str">
+        <v>279.583333333333</v>
+      </c>
+      <c r="I7" s="34" t="n">
         <f aca="false">IF($H7="","",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A7)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*(ROUND(Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30),6)=ROUND($H7,6))*Log!$B$4:$B$503)))</f>
-        <v/>
-      </c>
-      <c r="J7" s="34" t="str">
+        <v>4</v>
+      </c>
+      <c r="J7" s="34" t="n">
         <f aca="false">IF($D7="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A7)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*Log!$G$4:$G$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A7)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*Log!$G$4:$G$503))))</f>
-        <v/>
+        <v>3812.5</v>
       </c>
       <c r="K7" s="34" t="n">
         <f aca="false">IF($D7="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A7)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A7)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L7" s="37" t="n">
         <f aca="false">IF($K7="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A7)*(Log!$B$4:$B$503=$K7)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A7)*(Log!$B$4:$B$503=$K7)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>18</v>
-      </c>
-      <c r="M7" s="34" t="str">
+        <v>152.5</v>
+      </c>
+      <c r="M7" s="34" t="n">
         <f aca="false">IF($L7="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A7)*(Log!$B$4:$B$503=$K7)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503=$L7)*Log!$G$4:$G$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A7)*(Log!$B$4:$B$503=$K7)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503=$L7)*Log!$G$4:$G$503))))</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="N7" s="45" t="n">
-        <f aca="false">IF($L7="","",ROUND($L7*1.025*2,0)/2)</f>
-        <v>18.5</v>
+        <f aca="false">IF($L7&lt;&gt;"",IF(Übungen!$H7="",ROUND($L7*1.025*2,0)/2,MIN(ROUND($L7*1.025*2,0)/2,Übungen!$H7)),IF(Übungen!$G7="","",Übungen!$G7))</f>
+        <v>152.5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="str">
         <f aca="false">IF(Übungen!$A8="","",Übungen!$A8)</f>
-        <v>Kickback</v>
+        <v>Rumänisches Kreuzheben</v>
       </c>
       <c r="B8" s="43" t="str">
         <f aca="false">IF(Übungen!$B8="","",Übungen!$B8)</f>
         <v>Beine hinten</v>
       </c>
-      <c r="C8" s="31" t="n">
+      <c r="C8" s="31" t="str">
         <f aca="false">IF($D8="","",SUMPRODUCT((COUNTIFS(Log!$D$4:$D$503,$A8,Log!$E$4:$E$503,"A",Log!$B$4:$B$503,Einheiten!$A$4:$A$27)&gt;0)*1))</f>
-        <v>4</v>
-      </c>
-      <c r="D8" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D8" s="31" t="str">
         <f aca="false">IF($A8="","",IF(COUNTIFS(Log!$D$4:$D$503,$A8,Log!$E$4:$E$503,"A")=0,"",COUNTIFS(Log!$D$4:$D$503,$A8,Log!$E$4:$E$503,"A")))</f>
-        <v>8</v>
-      </c>
-      <c r="E8" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E8" s="31" t="str">
         <f aca="false">IF($D8="","",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A8,Log!$E$4:$E$503,"A"))</f>
-        <v>7119</v>
-      </c>
-      <c r="F8" s="44" t="n">
+        <v/>
+      </c>
+      <c r="F8" s="44" t="str">
         <f aca="false">IF($D8="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A8)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A8)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>84</v>
-      </c>
-      <c r="G8" s="31" t="n">
+        <v/>
+      </c>
+      <c r="G8" s="31" t="str">
         <f aca="false">IF($F8="","",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A8)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503=$F8)*Log!$B$4:$B$503)))</f>
-        <v>3</v>
-      </c>
-      <c r="H8" s="44" t="n">
+        <v/>
+      </c>
+      <c r="H8" s="44" t="str">
         <f aca="false">IF($D8="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A8)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A8)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v>117.6</v>
-      </c>
-      <c r="I8" s="31" t="n">
+        <v/>
+      </c>
+      <c r="I8" s="31" t="str">
         <f aca="false">IF($H8="","",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A8)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*(ROUND(Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30),6)=ROUND($H8,6))*Log!$B$4:$B$503)))</f>
-        <v>3</v>
-      </c>
-      <c r="J8" s="31" t="n">
+        <v/>
+      </c>
+      <c r="J8" s="31" t="str">
         <f aca="false">IF($D8="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A8)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*Log!$G$4:$G$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A8)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*Log!$G$4:$G$503))))</f>
-        <v>1078</v>
-      </c>
-      <c r="K8" s="31" t="n">
+        <v/>
+      </c>
+      <c r="K8" s="31" t="str">
         <f aca="false">IF($D8="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A8)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A8)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))))</f>
-        <v>4</v>
-      </c>
-      <c r="L8" s="35" t="n">
+        <v/>
+      </c>
+      <c r="L8" s="35" t="str">
         <f aca="false">IF($K8="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A8)*(Log!$B$4:$B$503=$K8)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A8)*(Log!$B$4:$B$503=$K8)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>63</v>
-      </c>
-      <c r="M8" s="31" t="n">
+        <v/>
+      </c>
+      <c r="M8" s="31" t="str">
         <f aca="false">IF($L8="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A8)*(Log!$B$4:$B$503=$K8)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503=$L8)*Log!$G$4:$G$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A8)*(Log!$B$4:$B$503=$K8)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503=$L8)*Log!$G$4:$G$503))))</f>
-        <v>15</v>
-      </c>
-      <c r="N8" s="44" t="n">
-        <f aca="false">IF($L8="","",ROUND($L8*1.025*2,0)/2)</f>
-        <v>64.5</v>
+        <v/>
+      </c>
+      <c r="N8" s="44" t="str">
+        <f aca="false">IF($L8&lt;&gt;"",IF(Übungen!$H8="",ROUND($L8*1.025*2,0)/2,MIN(ROUND($L8*1.025*2,0)/2,Übungen!$H8)),IF(Übungen!$G8="","",Übungen!$G8))</f>
+        <v/>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="str">
         <f aca="false">IF(Übungen!$A9="","",Übungen!$A9)</f>
-        <v>Seitliche Kickbacks</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="B9" s="4" t="str">
         <f aca="false">IF(Übungen!$B9="","",Übungen!$B9)</f>
@@ -23253,51 +23463,51 @@
       </c>
       <c r="C9" s="34" t="n">
         <f aca="false">IF($D9="","",SUMPRODUCT((COUNTIFS(Log!$D$4:$D$503,$A9,Log!$E$4:$E$503,"A",Log!$B$4:$B$503,Einheiten!$A$4:$A$27)&gt;0)*1))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D9" s="34" t="n">
         <f aca="false">IF($A9="","",IF(COUNTIFS(Log!$D$4:$D$503,$A9,Log!$E$4:$E$503,"A")=0,"",COUNTIFS(Log!$D$4:$D$503,$A9,Log!$E$4:$E$503,"A")))</f>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E9" s="34" t="n">
         <f aca="false">IF($D9="","",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A9,Log!$E$4:$E$503,"A"))</f>
-        <v>2053</v>
+        <v>20060</v>
       </c>
       <c r="F9" s="45" t="n">
         <f aca="false">IF($D9="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A9)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A9)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>49</v>
+        <v>280</v>
       </c>
       <c r="G9" s="34" t="n">
         <f aca="false">IF($F9="","",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A9)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503=$F9)*Log!$B$4:$B$503)))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H9" s="45" t="n">
         <f aca="false">IF($D9="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A9)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A9)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v>68.6</v>
+        <v>360</v>
       </c>
       <c r="I9" s="34" t="n">
         <f aca="false">IF($H9="","",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A9)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*(ROUND(Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30),6)=ROUND($H9,6))*Log!$B$4:$B$503)))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J9" s="34" t="n">
         <f aca="false">IF($D9="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A9)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*Log!$G$4:$G$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A9)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*Log!$G$4:$G$503))))</f>
-        <v>588</v>
+        <v>2700</v>
       </c>
       <c r="K9" s="34" t="n">
         <f aca="false">IF($D9="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A9)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A9)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L9" s="37" t="n">
         <f aca="false">IF($K9="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A9)*(Log!$B$4:$B$503=$K9)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A9)*(Log!$B$4:$B$503=$K9)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>35</v>
+        <v>270</v>
       </c>
       <c r="M9" s="34" t="n">
         <f aca="false">IF($L9="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A9)*(Log!$B$4:$B$503=$K9)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503=$L9)*Log!$G$4:$G$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A9)*(Log!$B$4:$B$503=$K9)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503=$L9)*Log!$G$4:$G$503))))</f>
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="N9" s="45" t="n">
-        <f aca="false">IF($L9="","",ROUND($L9*1.025*2,0)/2)</f>
-        <v>36</v>
+        <f aca="false">IF($L9&lt;&gt;"",IF(Übungen!$H9="",ROUND($L9*1.025*2,0)/2,MIN(ROUND($L9*1.025*2,0)/2,Übungen!$H9)),IF(Übungen!$G9="","",Übungen!$G9))</f>
+        <v>277</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23354,14 +23564,14 @@
         <v>15</v>
       </c>
       <c r="N10" s="44" t="n">
-        <f aca="false">IF($L10="","",ROUND($L10*1.025*2,0)/2)</f>
+        <f aca="false">IF($L10&lt;&gt;"",IF(Übungen!$H10="",ROUND($L10*1.025*2,0)/2,MIN(ROUND($L10*1.025*2,0)/2,Übungen!$H10)),IF(Übungen!$G10="","",Übungen!$G10))</f>
         <v>46</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="str">
         <f aca="false">IF(Übungen!$A11="","",Übungen!$A11)</f>
-        <v>Hip Thrust</v>
+        <v>Seitliche Kickbacks</v>
       </c>
       <c r="B11" s="4" t="str">
         <f aca="false">IF(Übungen!$B11="","",Übungen!$B11)</f>
@@ -23369,51 +23579,51 @@
       </c>
       <c r="C11" s="34" t="n">
         <f aca="false">IF($D11="","",SUMPRODUCT((COUNTIFS(Log!$D$4:$D$503,$A11,Log!$E$4:$E$503,"A",Log!$B$4:$B$503,Einheiten!$A$4:$A$27)&gt;0)*1))</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D11" s="34" t="n">
         <f aca="false">IF($A11="","",IF(COUNTIFS(Log!$D$4:$D$503,$A11,Log!$E$4:$E$503,"A")=0,"",COUNTIFS(Log!$D$4:$D$503,$A11,Log!$E$4:$E$503,"A")))</f>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E11" s="34" t="n">
         <f aca="false">IF($D11="","",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A11,Log!$E$4:$E$503,"A"))</f>
-        <v>20060</v>
+        <v>2053</v>
       </c>
       <c r="F11" s="45" t="n">
         <f aca="false">IF($D11="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A11)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A11)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>280</v>
+        <v>49</v>
       </c>
       <c r="G11" s="34" t="n">
         <f aca="false">IF($F11="","",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A11)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503=$F11)*Log!$B$4:$B$503)))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H11" s="45" t="n">
         <f aca="false">IF($D11="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A11)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A11)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v>360</v>
+        <v>68.6</v>
       </c>
       <c r="I11" s="34" t="n">
         <f aca="false">IF($H11="","",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A11)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*(ROUND(Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30),6)=ROUND($H11,6))*Log!$B$4:$B$503)))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J11" s="34" t="n">
         <f aca="false">IF($D11="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A11)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*Log!$G$4:$G$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A11)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*Log!$G$4:$G$503))))</f>
-        <v>2700</v>
+        <v>588</v>
       </c>
       <c r="K11" s="34" t="n">
         <f aca="false">IF($D11="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A11)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A11)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))))</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L11" s="37" t="n">
         <f aca="false">IF($K11="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A11)*(Log!$B$4:$B$503=$K11)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A11)*(Log!$B$4:$B$503=$K11)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v>270</v>
+        <v>35</v>
       </c>
       <c r="M11" s="34" t="n">
         <f aca="false">IF($L11="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A11)*(Log!$B$4:$B$503=$K11)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503=$L11)*Log!$G$4:$G$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A11)*(Log!$B$4:$B$503=$K11)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503=$L11)*Log!$G$4:$G$503))))</f>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="N11" s="45" t="n">
-        <f aca="false">IF($L11="","",ROUND($L11*1.025*2,0)/2)</f>
-        <v>277</v>
+        <f aca="false">IF($L11&lt;&gt;"",IF(Übungen!$H11="",ROUND($L11*1.025*2,0)/2,MIN(ROUND($L11*1.025*2,0)/2,Übungen!$H11)),IF(Übungen!$G11="","",Übungen!$G11))</f>
+        <v>36</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23470,38 +23680,38 @@
         <v>12</v>
       </c>
       <c r="N12" s="44" t="n">
-        <f aca="false">IF($L12="","",ROUND($L12*1.025*2,0)/2)</f>
+        <f aca="false">IF($L12&lt;&gt;"",IF(Übungen!$H12="",ROUND($L12*1.025*2,0)/2,MIN(ROUND($L12*1.025*2,0)/2,Übungen!$H12)),IF(Übungen!$G12="","",Übungen!$G12))</f>
         <v>154</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="str">
         <f aca="false">IF(Übungen!$A13="","",Übungen!$A13)</f>
-        <v/>
+        <v>Lunges</v>
       </c>
       <c r="B13" s="4" t="str">
         <f aca="false">IF(Übungen!$B13="","",Übungen!$B13)</f>
-        <v/>
-      </c>
-      <c r="C13" s="34" t="str">
+        <v>Beine vorne</v>
+      </c>
+      <c r="C13" s="34" t="n">
         <f aca="false">IF($D13="","",SUMPRODUCT((COUNTIFS(Log!$D$4:$D$503,$A13,Log!$E$4:$E$503,"A",Log!$B$4:$B$503,Einheiten!$A$4:$A$27)&gt;0)*1))</f>
-        <v/>
-      </c>
-      <c r="D13" s="34" t="str">
+        <v>3</v>
+      </c>
+      <c r="D13" s="34" t="n">
         <f aca="false">IF($A13="","",IF(COUNTIFS(Log!$D$4:$D$503,$A13,Log!$E$4:$E$503,"A")=0,"",COUNTIFS(Log!$D$4:$D$503,$A13,Log!$E$4:$E$503,"A")))</f>
-        <v/>
-      </c>
-      <c r="E13" s="34" t="str">
+        <v>3</v>
+      </c>
+      <c r="E13" s="34" t="n">
         <f aca="false">IF($D13="","",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A13,Log!$E$4:$E$503,"A"))</f>
-        <v/>
-      </c>
-      <c r="F13" s="45" t="str">
+        <v>0</v>
+      </c>
+      <c r="F13" s="45" t="n">
         <f aca="false">IF($D13="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A13)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A13)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v/>
-      </c>
-      <c r="G13" s="34" t="str">
+        <v>18</v>
+      </c>
+      <c r="G13" s="34" t="n">
         <f aca="false">IF($F13="","",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A13)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503=$F13)*Log!$B$4:$B$503)))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="H13" s="45" t="str">
         <f aca="false">IF($D13="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A13)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A13)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
@@ -23515,79 +23725,79 @@
         <f aca="false">IF($D13="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A13)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*Log!$G$4:$G$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A13)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*Log!$G$4:$G$503))))</f>
         <v/>
       </c>
-      <c r="K13" s="34" t="str">
+      <c r="K13" s="34" t="n">
         <f aca="false">IF($D13="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A13)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A13)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))))</f>
-        <v/>
-      </c>
-      <c r="L13" s="37" t="str">
+        <v>3</v>
+      </c>
+      <c r="L13" s="37" t="n">
         <f aca="false">IF($K13="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A13)*(Log!$B$4:$B$503=$K13)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A13)*(Log!$B$4:$B$503=$K13)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="M13" s="34" t="str">
         <f aca="false">IF($L13="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A13)*(Log!$B$4:$B$503=$K13)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503=$L13)*Log!$G$4:$G$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A13)*(Log!$B$4:$B$503=$K13)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503=$L13)*Log!$G$4:$G$503))))</f>
         <v/>
       </c>
-      <c r="N13" s="45" t="str">
-        <f aca="false">IF($L13="","",ROUND($L13*1.025*2,0)/2)</f>
-        <v/>
+      <c r="N13" s="45" t="n">
+        <f aca="false">IF($L13&lt;&gt;"",IF(Übungen!$H13="",ROUND($L13*1.025*2,0)/2,MIN(ROUND($L13*1.025*2,0)/2,Übungen!$H13)),IF(Übungen!$G13="","",Übungen!$G13))</f>
+        <v>18.5</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="30" t="str">
         <f aca="false">IF(Übungen!$A14="","",Übungen!$A14)</f>
-        <v/>
+        <v>Kickback</v>
       </c>
       <c r="B14" s="43" t="str">
         <f aca="false">IF(Übungen!$B14="","",Übungen!$B14)</f>
-        <v/>
-      </c>
-      <c r="C14" s="31" t="str">
+        <v>Beine hinten</v>
+      </c>
+      <c r="C14" s="31" t="n">
         <f aca="false">IF($D14="","",SUMPRODUCT((COUNTIFS(Log!$D$4:$D$503,$A14,Log!$E$4:$E$503,"A",Log!$B$4:$B$503,Einheiten!$A$4:$A$27)&gt;0)*1))</f>
-        <v/>
-      </c>
-      <c r="D14" s="31" t="str">
+        <v>4</v>
+      </c>
+      <c r="D14" s="31" t="n">
         <f aca="false">IF($A14="","",IF(COUNTIFS(Log!$D$4:$D$503,$A14,Log!$E$4:$E$503,"A")=0,"",COUNTIFS(Log!$D$4:$D$503,$A14,Log!$E$4:$E$503,"A")))</f>
-        <v/>
-      </c>
-      <c r="E14" s="31" t="str">
+        <v>8</v>
+      </c>
+      <c r="E14" s="31" t="n">
         <f aca="false">IF($D14="","",SUMIFS(Log!$I$4:$I$503,Log!$D$4:$D$503,$A14,Log!$E$4:$E$503,"A"))</f>
-        <v/>
-      </c>
-      <c r="F14" s="44" t="str">
+        <v>7119</v>
+      </c>
+      <c r="F14" s="44" t="n">
         <f aca="false">IF($D14="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A14)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A14)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v/>
-      </c>
-      <c r="G14" s="31" t="str">
+        <v>84</v>
+      </c>
+      <c r="G14" s="31" t="n">
         <f aca="false">IF($F14="","",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A14)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503=$F14)*Log!$B$4:$B$503)))</f>
-        <v/>
-      </c>
-      <c r="H14" s="44" t="str">
+        <v>3</v>
+      </c>
+      <c r="H14" s="44" t="n">
         <f aca="false">IF($D14="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A14)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A14)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30)))))</f>
-        <v/>
-      </c>
-      <c r="I14" s="31" t="str">
+        <v>117.6</v>
+      </c>
+      <c r="I14" s="31" t="n">
         <f aca="false">IF($H14="","",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A14)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*(ROUND(Log!$F$4:$F$503*(1+Log!$G$4:$G$503/30),6)=ROUND($H14,6))*Log!$B$4:$B$503)))</f>
-        <v/>
-      </c>
-      <c r="J14" s="31" t="str">
+        <v>3</v>
+      </c>
+      <c r="J14" s="31" t="n">
         <f aca="false">IF($D14="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A14)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*Log!$G$4:$G$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A14)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*(Log!$G$4:$G$503&lt;&gt;"")*Log!$F$4:$F$503*Log!$G$4:$G$503))))</f>
-        <v/>
-      </c>
-      <c r="K14" s="31" t="str">
+        <v>1078</v>
+      </c>
+      <c r="K14" s="31" t="n">
         <f aca="false">IF($D14="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A14)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A14)*(Log!$E$4:$E$503="A")*Log!$B$4:$B$503))))</f>
-        <v/>
-      </c>
-      <c r="L14" s="35" t="str">
+        <v>4</v>
+      </c>
+      <c r="L14" s="35" t="n">
         <f aca="false">IF($K14="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A14)*(Log!$B$4:$B$503=$K14)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A14)*(Log!$B$4:$B$503=$K14)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503&lt;&gt;"")*Log!$F$4:$F$503))))</f>
-        <v/>
-      </c>
-      <c r="M14" s="31" t="str">
+        <v>63</v>
+      </c>
+      <c r="M14" s="31" t="n">
         <f aca="false">IF($L14="","",IF(SUMPRODUCT(MAX((Log!$D$4:$D$503=$A14)*(Log!$B$4:$B$503=$K14)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503=$L14)*Log!$G$4:$G$503))=0,"",SUMPRODUCT(MAX((Log!$D$4:$D$503=$A14)*(Log!$B$4:$B$503=$K14)*(Log!$E$4:$E$503="A")*(Log!$F$4:$F$503=$L14)*Log!$G$4:$G$503))))</f>
-        <v/>
-      </c>
-      <c r="N14" s="44" t="str">
-        <f aca="false">IF($L14="","",ROUND($L14*1.025*2,0)/2)</f>
-        <v/>
+        <v>15</v>
+      </c>
+      <c r="N14" s="44" t="n">
+        <f aca="false">IF($L14&lt;&gt;"",IF(Übungen!$H14="",ROUND($L14*1.025*2,0)/2,MIN(ROUND($L14*1.025*2,0)/2,Übungen!$H14)),IF(Übungen!$G14="","",Übungen!$G14))</f>
+        <v>64.5</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23644,7 +23854,7 @@
         <v/>
       </c>
       <c r="N15" s="45" t="str">
-        <f aca="false">IF($L15="","",ROUND($L15*1.025*2,0)/2)</f>
+        <f aca="false">IF($L15&lt;&gt;"",IF(Übungen!$H15="",ROUND($L15*1.025*2,0)/2,MIN(ROUND($L15*1.025*2,0)/2,Übungen!$H15)),IF(Übungen!$G15="","",Übungen!$G15))</f>
         <v/>
       </c>
     </row>
@@ -23702,7 +23912,7 @@
         <v/>
       </c>
       <c r="N16" s="44" t="str">
-        <f aca="false">IF($L16="","",ROUND($L16*1.025*2,0)/2)</f>
+        <f aca="false">IF($L16&lt;&gt;"",IF(Übungen!$H16="",ROUND($L16*1.025*2,0)/2,MIN(ROUND($L16*1.025*2,0)/2,Übungen!$H16)),IF(Übungen!$G16="","",Übungen!$G16))</f>
         <v/>
       </c>
     </row>
@@ -23760,13 +23970,13 @@
         <v/>
       </c>
       <c r="N17" s="45" t="str">
-        <f aca="false">IF($L17="","",ROUND($L17*1.025*2,0)/2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF($L17&lt;&gt;"",IF(Übungen!$H17="",ROUND($L17*1.025*2,0)/2,MIN(ROUND($L17*1.025*2,0)/2,Übungen!$H17)),IF(Übungen!$G17="","",Übungen!$G17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="42" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B19" s="42"/>
       <c r="C19" s="42"/>
@@ -23788,6 +23998,11 @@
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A19:N19"/>
   </mergeCells>
+  <conditionalFormatting sqref="A4:N17">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>Übungen!$I4="nein"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.5" right="0.4" top="0.7" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -23817,7 +24032,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -23829,21 +24044,21 @@
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="46" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B2" s="46"/>
       <c r="C2" s="47" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="E2" s="46" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="F2" s="46"/>
       <c r="G2" s="46" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="H2" s="46"/>
     </row>
@@ -23860,7 +24075,7 @@
     <row r="5" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="49" t="str">
         <f aca="false">Übungen!$A$4</f>
-        <v>Adduktion</v>
+        <v>Hackenschmidt-Kniebeuge</v>
       </c>
       <c r="B5" s="49"/>
       <c r="C5" s="49"/>
@@ -23872,8 +24087,8 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="50" t="str">
-        <f aca="false">IF(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$4,Rekorde!$A$4:$A$17,0)),"")="","noch keine Werte erfasst","Zuletzt: "&amp;TEXT(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$4,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg × "&amp;IF(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$4,Rekorde!$A$4:$A$17,0)),"")="","?",TEXT(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$4,Rekorde!$A$4:$A$17,0)),""),"0"))&amp;" Wdh     ·     Bestwert: "&amp;TEXT(IFERROR(INDEX(Rekorde!$F$4:$F$17,MATCH(Übungen!$A$4,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     Ziel heute: "&amp;TEXT(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$4,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     Ziel-Wdh: "&amp;Übungen!$D$4)</f>
-        <v>Zuletzt: 152.5 kg × 25 Wdh     ·     Bestwert: 152.5 kg     ·     Ziel heute: 156.5 kg     ·     Ziel-Wdh: 15-20</v>
+        <f aca="false">IF(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$4,Rekorde!$A$4:$A$17,0)),"")="",IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$4,Rekorde!$A$4:$A$17,0)),"")="","Neu im Plan - Startgewicht im Blatt 'Übungen' eintragen     ·     ","Neu im Plan     ·     Start: "&amp;TEXT(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$4,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     "),"Zuletzt: "&amp;TEXT(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$4,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg × "&amp;IF(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$4,Rekorde!$A$4:$A$17,0)),"")="","?",TEXT(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$4,Rekorde!$A$4:$A$17,0)),""),"0"))&amp;" Wdh     ·     Bestwert: "&amp;TEXT(IFERROR(INDEX(Rekorde!$F$4:$F$17,MATCH(Übungen!$A$4,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     "&amp;IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$4,Rekorde!$A$4:$A$17,0)),"")="","","Ziel heute: "&amp;TEXT(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$4,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     ")&amp;IF(AND(Übungen!$H$4&lt;&gt;"",IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$4,Rekorde!$A$4:$A$17,0)),"")&lt;&gt;"",IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$4,Rekorde!$A$4:$A$17,0)),"")&gt;=Übungen!$H$4),"Stackende, über Tempo und Pausen steigern     ·     ",""))&amp;"Vorgabe: "&amp;Übungen!$E$4&amp;" × "&amp;Übungen!$D$4&amp;" Wdh @ RPE "&amp;Übungen!$F$4</f>
+        <v>Neu im Plan - Startgewicht im Blatt 'Übungen' eintragen     ·     Vorgabe: 3 × 6-10 Wdh @ RPE 8-9</v>
       </c>
       <c r="B6" s="50"/>
       <c r="C6" s="50"/>
@@ -23885,28 +24100,28 @@
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="51" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B7" s="51" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C7" s="51" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="D7" s="51" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="E7" s="51" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F7" s="51" t="s">
         <v>39</v>
       </c>
       <c r="G7" s="51" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="H7" s="51" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23914,11 +24129,11 @@
         <v>1</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>91</v>
-      </c>
-      <c r="C8" s="54" t="n">
+        <v>97</v>
+      </c>
+      <c r="C8" s="54" t="str">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$4,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$4,Rekorde!$A$4:$A$17,0)),"")*0.45*2,0)/2)</f>
-        <v>70.5</v>
+        <v/>
       </c>
       <c r="D8" s="55"/>
       <c r="E8" s="55"/>
@@ -23931,11 +24146,11 @@
         <v>2</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>91</v>
-      </c>
-      <c r="C9" s="54" t="n">
+        <v>97</v>
+      </c>
+      <c r="C9" s="54" t="str">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$4,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$4,Rekorde!$A$4:$A$17,0)),"")*0.7*2,0)/2)</f>
-        <v>109.5</v>
+        <v/>
       </c>
       <c r="D9" s="55"/>
       <c r="E9" s="55"/>
@@ -23948,11 +24163,11 @@
         <v>3</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>92</v>
-      </c>
-      <c r="C10" s="54" t="n">
+        <v>98</v>
+      </c>
+      <c r="C10" s="54" t="str">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$4,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$4,Rekorde!$A$4:$A$17,0)),"")*1*2,0)/2)</f>
-        <v>156.5</v>
+        <v/>
       </c>
       <c r="D10" s="55"/>
       <c r="E10" s="55"/>
@@ -23965,11 +24180,11 @@
         <v>4</v>
       </c>
       <c r="B11" s="56" t="s">
-        <v>92</v>
-      </c>
-      <c r="C11" s="54" t="n">
+        <v>98</v>
+      </c>
+      <c r="C11" s="54" t="str">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$4,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$4,Rekorde!$A$4:$A$17,0)),"")*1*2,0)/2)</f>
-        <v>156.5</v>
+        <v/>
       </c>
       <c r="D11" s="55"/>
       <c r="E11" s="55"/>
@@ -23981,10 +24196,13 @@
       <c r="A12" s="52" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="53" t="s">
-        <v>93</v>
-      </c>
-      <c r="C12" s="57"/>
+      <c r="B12" s="56" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="54" t="str">
+        <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$4,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$4,Rekorde!$A$4:$A$17,0)),"")*1*2,0)/2)</f>
+        <v/>
+      </c>
       <c r="D12" s="55"/>
       <c r="E12" s="55"/>
       <c r="F12" s="55"/>
@@ -23994,7 +24212,7 @@
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="49" t="str">
         <f aca="false">Übungen!$A$5</f>
-        <v>Beinstrecker</v>
+        <v>Split Squat</v>
       </c>
       <c r="B14" s="49"/>
       <c r="C14" s="49"/>
@@ -24006,8 +24224,8 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="50" t="str">
-        <f aca="false">IF(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$5,Rekorde!$A$4:$A$17,0)),"")="","noch keine Werte erfasst","Zuletzt: "&amp;TEXT(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$5,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg × "&amp;IF(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$5,Rekorde!$A$4:$A$17,0)),"")="","?",TEXT(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$5,Rekorde!$A$4:$A$17,0)),""),"0"))&amp;" Wdh     ·     Bestwert: "&amp;TEXT(IFERROR(INDEX(Rekorde!$F$4:$F$17,MATCH(Übungen!$A$5,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     Ziel heute: "&amp;TEXT(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$5,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     Ziel-Wdh: "&amp;Übungen!$D$5)</f>
-        <v>Zuletzt: 80 kg × 12 Wdh     ·     Bestwert: 85 kg     ·     Ziel heute: 82 kg     ·     Ziel-Wdh: 8-12</v>
+        <f aca="false">IF(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$5,Rekorde!$A$4:$A$17,0)),"")="",IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$5,Rekorde!$A$4:$A$17,0)),"")="","Neu im Plan - Startgewicht im Blatt 'Übungen' eintragen     ·     ","Neu im Plan     ·     Start: "&amp;TEXT(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$5,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     "),"Zuletzt: "&amp;TEXT(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$5,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg × "&amp;IF(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$5,Rekorde!$A$4:$A$17,0)),"")="","?",TEXT(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$5,Rekorde!$A$4:$A$17,0)),""),"0"))&amp;" Wdh     ·     Bestwert: "&amp;TEXT(IFERROR(INDEX(Rekorde!$F$4:$F$17,MATCH(Übungen!$A$5,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     "&amp;IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$5,Rekorde!$A$4:$A$17,0)),"")="","","Ziel heute: "&amp;TEXT(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$5,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     ")&amp;IF(AND(Übungen!$H$5&lt;&gt;"",IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$5,Rekorde!$A$4:$A$17,0)),"")&lt;&gt;"",IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$5,Rekorde!$A$4:$A$17,0)),"")&gt;=Übungen!$H$5),"Stackende, über Tempo und Pausen steigern     ·     ",""))&amp;"Vorgabe: "&amp;Übungen!$E$5&amp;" × "&amp;Übungen!$D$5&amp;" Wdh @ RPE "&amp;Übungen!$F$5</f>
+        <v>Zuletzt: 80 kg × 8 Wdh     ·     Bestwert: 105 kg     ·     Ziel heute: 82 kg     ·     Vorgabe: 3 × 8-10 Wdh @ RPE 8</v>
       </c>
       <c r="B15" s="50"/>
       <c r="C15" s="50"/>
@@ -24019,28 +24237,28 @@
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="51" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B16" s="51" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="D16" s="51" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="E16" s="51" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F16" s="51" t="s">
         <v>39</v>
       </c>
       <c r="G16" s="51" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="H16" s="51" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24048,7 +24266,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="53" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C17" s="54" t="n">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$5,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$5,Rekorde!$A$4:$A$17,0)),"")*0.45*2,0)/2)</f>
@@ -24065,7 +24283,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="53" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C18" s="54" t="n">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$5,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$5,Rekorde!$A$4:$A$17,0)),"")*0.7*2,0)/2)</f>
@@ -24082,7 +24300,7 @@
         <v>3</v>
       </c>
       <c r="B19" s="56" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C19" s="54" t="n">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$5,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$5,Rekorde!$A$4:$A$17,0)),"")*1*2,0)/2)</f>
@@ -24099,7 +24317,7 @@
         <v>4</v>
       </c>
       <c r="B20" s="56" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C20" s="54" t="n">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$5,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$5,Rekorde!$A$4:$A$17,0)),"")*1*2,0)/2)</f>
@@ -24115,10 +24333,13 @@
       <c r="A21" s="52" t="n">
         <v>5</v>
       </c>
-      <c r="B21" s="53" t="s">
-        <v>93</v>
-      </c>
-      <c r="C21" s="57"/>
+      <c r="B21" s="56" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" s="54" t="n">
+        <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$5,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$5,Rekorde!$A$4:$A$17,0)),"")*1*2,0)/2)</f>
+        <v>82</v>
+      </c>
       <c r="D21" s="55"/>
       <c r="E21" s="55"/>
       <c r="F21" s="55"/>
@@ -24128,7 +24349,7 @@
     <row r="23" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="49" t="str">
         <f aca="false">Übungen!$A$6</f>
-        <v>Split Squat</v>
+        <v>Beinstrecker</v>
       </c>
       <c r="B23" s="49"/>
       <c r="C23" s="49"/>
@@ -24140,8 +24361,8 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="50" t="str">
-        <f aca="false">IF(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$6,Rekorde!$A$4:$A$17,0)),"")="","noch keine Werte erfasst","Zuletzt: "&amp;TEXT(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$6,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg × "&amp;IF(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$6,Rekorde!$A$4:$A$17,0)),"")="","?",TEXT(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$6,Rekorde!$A$4:$A$17,0)),""),"0"))&amp;" Wdh     ·     Bestwert: "&amp;TEXT(IFERROR(INDEX(Rekorde!$F$4:$F$17,MATCH(Übungen!$A$6,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     Ziel heute: "&amp;TEXT(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$6,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     Ziel-Wdh: "&amp;Übungen!$D$6)</f>
-        <v>Zuletzt: 80 kg × 8 Wdh     ·     Bestwert: 105 kg     ·     Ziel heute: 82 kg     ·     Ziel-Wdh: 5-8</v>
+        <f aca="false">IF(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$6,Rekorde!$A$4:$A$17,0)),"")="",IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$6,Rekorde!$A$4:$A$17,0)),"")="","Neu im Plan - Startgewicht im Blatt 'Übungen' eintragen     ·     ","Neu im Plan     ·     Start: "&amp;TEXT(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$6,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     "),"Zuletzt: "&amp;TEXT(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$6,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg × "&amp;IF(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$6,Rekorde!$A$4:$A$17,0)),"")="","?",TEXT(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$6,Rekorde!$A$4:$A$17,0)),""),"0"))&amp;" Wdh     ·     Bestwert: "&amp;TEXT(IFERROR(INDEX(Rekorde!$F$4:$F$17,MATCH(Übungen!$A$6,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     "&amp;IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$6,Rekorde!$A$4:$A$17,0)),"")="","","Ziel heute: "&amp;TEXT(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$6,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     ")&amp;IF(AND(Übungen!$H$6&lt;&gt;"",IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$6,Rekorde!$A$4:$A$17,0)),"")&lt;&gt;"",IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$6,Rekorde!$A$4:$A$17,0)),"")&gt;=Übungen!$H$6),"Stackende, über Tempo und Pausen steigern     ·     ",""))&amp;"Vorgabe: "&amp;Übungen!$E$6&amp;" × "&amp;Übungen!$D$6&amp;" Wdh @ RPE "&amp;Übungen!$F$6</f>
+        <v>Zuletzt: 80 kg × 12 Wdh     ·     Bestwert: 85 kg     ·     Ziel heute: 82 kg     ·     Vorgabe: 3 × 12-15 Wdh @ RPE 9</v>
       </c>
       <c r="B24" s="50"/>
       <c r="C24" s="50"/>
@@ -24153,28 +24374,28 @@
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="51" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B25" s="51" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C25" s="51" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="D25" s="51" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="E25" s="51" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F25" s="51" t="s">
         <v>39</v>
       </c>
       <c r="G25" s="51" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="H25" s="51" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24182,7 +24403,7 @@
         <v>1</v>
       </c>
       <c r="B26" s="53" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C26" s="54" t="n">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$6,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$6,Rekorde!$A$4:$A$17,0)),"")*0.45*2,0)/2)</f>
@@ -24199,7 +24420,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="53" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C27" s="54" t="n">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$6,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$6,Rekorde!$A$4:$A$17,0)),"")*0.7*2,0)/2)</f>
@@ -24216,7 +24437,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="56" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C28" s="54" t="n">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$6,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$6,Rekorde!$A$4:$A$17,0)),"")*1*2,0)/2)</f>
@@ -24233,7 +24454,7 @@
         <v>4</v>
       </c>
       <c r="B29" s="56" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C29" s="54" t="n">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$6,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$6,Rekorde!$A$4:$A$17,0)),"")*1*2,0)/2)</f>
@@ -24250,7 +24471,7 @@
         <v>5</v>
       </c>
       <c r="B30" s="53" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C30" s="57"/>
       <c r="D30" s="55"/>
@@ -24262,7 +24483,7 @@
     <row r="32" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="49" t="str">
         <f aca="false">Übungen!$A$7</f>
-        <v>Lunges</v>
+        <v>Adduktion</v>
       </c>
       <c r="B32" s="49"/>
       <c r="C32" s="49"/>
@@ -24274,8 +24495,8 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="50" t="str">
-        <f aca="false">IF(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$7,Rekorde!$A$4:$A$17,0)),"")="","noch keine Werte erfasst","Zuletzt: "&amp;TEXT(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$7,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg × "&amp;IF(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$7,Rekorde!$A$4:$A$17,0)),"")="","?",TEXT(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$7,Rekorde!$A$4:$A$17,0)),""),"0"))&amp;" Wdh     ·     Bestwert: "&amp;TEXT(IFERROR(INDEX(Rekorde!$F$4:$F$17,MATCH(Übungen!$A$7,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     Ziel heute: "&amp;TEXT(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$7,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     Ziel-Wdh: "&amp;Übungen!$D$7)</f>
-        <v>Zuletzt: 18 kg × ? Wdh     ·     Bestwert: 18 kg     ·     Ziel heute: 18.5 kg     ·     Ziel-Wdh: 10-12</v>
+        <f aca="false">IF(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$7,Rekorde!$A$4:$A$17,0)),"")="",IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$7,Rekorde!$A$4:$A$17,0)),"")="","Neu im Plan - Startgewicht im Blatt 'Übungen' eintragen     ·     ","Neu im Plan     ·     Start: "&amp;TEXT(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$7,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     "),"Zuletzt: "&amp;TEXT(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$7,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg × "&amp;IF(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$7,Rekorde!$A$4:$A$17,0)),"")="","?",TEXT(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$7,Rekorde!$A$4:$A$17,0)),""),"0"))&amp;" Wdh     ·     Bestwert: "&amp;TEXT(IFERROR(INDEX(Rekorde!$F$4:$F$17,MATCH(Übungen!$A$7,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     "&amp;IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$7,Rekorde!$A$4:$A$17,0)),"")="","","Ziel heute: "&amp;TEXT(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$7,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     ")&amp;IF(AND(Übungen!$H$7&lt;&gt;"",IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$7,Rekorde!$A$4:$A$17,0)),"")&lt;&gt;"",IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$7,Rekorde!$A$4:$A$17,0)),"")&gt;=Übungen!$H$7),"Stackende, über Tempo und Pausen steigern     ·     ",""))&amp;"Vorgabe: "&amp;Übungen!$E$7&amp;" × "&amp;Übungen!$D$7&amp;" Wdh @ RPE "&amp;Übungen!$F$7</f>
+        <v>Zuletzt: 152.5 kg × 25 Wdh     ·     Bestwert: 152.5 kg     ·     Ziel heute: 152.5 kg     ·     Stackende, über Tempo und Pausen steigern     ·     Vorgabe: 3 × 15-20 Wdh @ RPE 9</v>
       </c>
       <c r="B33" s="50"/>
       <c r="C33" s="50"/>
@@ -24287,28 +24508,28 @@
     </row>
     <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="51" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B34" s="51" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C34" s="51" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="D34" s="51" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="E34" s="51" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F34" s="51" t="s">
         <v>39</v>
       </c>
       <c r="G34" s="51" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="H34" s="51" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24316,11 +24537,11 @@
         <v>1</v>
       </c>
       <c r="B35" s="53" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C35" s="54" t="n">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$7,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$7,Rekorde!$A$4:$A$17,0)),"")*0.45*2,0)/2)</f>
-        <v>8.5</v>
+        <v>68.5</v>
       </c>
       <c r="D35" s="55"/>
       <c r="E35" s="55"/>
@@ -24333,11 +24554,11 @@
         <v>2</v>
       </c>
       <c r="B36" s="53" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C36" s="54" t="n">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$7,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$7,Rekorde!$A$4:$A$17,0)),"")*0.7*2,0)/2)</f>
-        <v>13</v>
+        <v>107</v>
       </c>
       <c r="D36" s="55"/>
       <c r="E36" s="55"/>
@@ -24350,11 +24571,11 @@
         <v>3</v>
       </c>
       <c r="B37" s="56" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C37" s="54" t="n">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$7,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$7,Rekorde!$A$4:$A$17,0)),"")*1*2,0)/2)</f>
-        <v>18.5</v>
+        <v>152.5</v>
       </c>
       <c r="D37" s="55"/>
       <c r="E37" s="55"/>
@@ -24367,11 +24588,11 @@
         <v>4</v>
       </c>
       <c r="B38" s="56" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C38" s="54" t="n">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$7,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$7,Rekorde!$A$4:$A$17,0)),"")*1*2,0)/2)</f>
-        <v>18.5</v>
+        <v>152.5</v>
       </c>
       <c r="D38" s="55"/>
       <c r="E38" s="55"/>
@@ -24384,7 +24605,7 @@
         <v>5</v>
       </c>
       <c r="B39" s="53" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C39" s="57"/>
       <c r="D39" s="55"/>
@@ -24395,7 +24616,7 @@
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -24437,7 +24658,7 @@
     </row>
     <row r="46" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -24449,21 +24670,21 @@
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="46" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B47" s="46"/>
       <c r="C47" s="47" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D47" s="47" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="E47" s="46" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="F47" s="46"/>
       <c r="G47" s="46" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="H47" s="46"/>
     </row>
@@ -24480,7 +24701,7 @@
     <row r="50" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="49" t="str">
         <f aca="false">Übungen!$A$8</f>
-        <v>Kickback</v>
+        <v>Rumänisches Kreuzheben</v>
       </c>
       <c r="B50" s="49"/>
       <c r="C50" s="49"/>
@@ -24492,8 +24713,8 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="50" t="str">
-        <f aca="false">IF(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$8,Rekorde!$A$4:$A$17,0)),"")="","noch keine Werte erfasst","Zuletzt: "&amp;TEXT(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$8,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg × "&amp;IF(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$8,Rekorde!$A$4:$A$17,0)),"")="","?",TEXT(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$8,Rekorde!$A$4:$A$17,0)),""),"0"))&amp;" Wdh     ·     Bestwert: "&amp;TEXT(IFERROR(INDEX(Rekorde!$F$4:$F$17,MATCH(Übungen!$A$8,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     Ziel heute: "&amp;TEXT(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$8,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     Ziel-Wdh: "&amp;Übungen!$D$8)</f>
-        <v>Zuletzt: 63 kg × 15 Wdh     ·     Bestwert: 84 kg     ·     Ziel heute: 64.5 kg     ·     Ziel-Wdh: 10-15</v>
+        <f aca="false">IF(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$8,Rekorde!$A$4:$A$17,0)),"")="",IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$8,Rekorde!$A$4:$A$17,0)),"")="","Neu im Plan - Startgewicht im Blatt 'Übungen' eintragen     ·     ","Neu im Plan     ·     Start: "&amp;TEXT(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$8,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     "),"Zuletzt: "&amp;TEXT(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$8,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg × "&amp;IF(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$8,Rekorde!$A$4:$A$17,0)),"")="","?",TEXT(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$8,Rekorde!$A$4:$A$17,0)),""),"0"))&amp;" Wdh     ·     Bestwert: "&amp;TEXT(IFERROR(INDEX(Rekorde!$F$4:$F$17,MATCH(Übungen!$A$8,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     "&amp;IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$8,Rekorde!$A$4:$A$17,0)),"")="","","Ziel heute: "&amp;TEXT(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$8,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     ")&amp;IF(AND(Übungen!$H$8&lt;&gt;"",IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$8,Rekorde!$A$4:$A$17,0)),"")&lt;&gt;"",IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$8,Rekorde!$A$4:$A$17,0)),"")&gt;=Übungen!$H$8),"Stackende, über Tempo und Pausen steigern     ·     ",""))&amp;"Vorgabe: "&amp;Übungen!$E$8&amp;" × "&amp;Übungen!$D$8&amp;" Wdh @ RPE "&amp;Übungen!$F$8</f>
+        <v>Neu im Plan - Startgewicht im Blatt 'Übungen' eintragen     ·     Vorgabe: 3 × 8-10 Wdh @ RPE 8</v>
       </c>
       <c r="B51" s="50"/>
       <c r="C51" s="50"/>
@@ -24505,28 +24726,28 @@
     </row>
     <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="51" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B52" s="51" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C52" s="51" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="D52" s="51" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="E52" s="51" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F52" s="51" t="s">
         <v>39</v>
       </c>
       <c r="G52" s="51" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="H52" s="51" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24534,11 +24755,11 @@
         <v>1</v>
       </c>
       <c r="B53" s="53" t="s">
-        <v>91</v>
-      </c>
-      <c r="C53" s="54" t="n">
+        <v>97</v>
+      </c>
+      <c r="C53" s="54" t="str">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$8,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$8,Rekorde!$A$4:$A$17,0)),"")*0.45*2,0)/2)</f>
-        <v>29</v>
+        <v/>
       </c>
       <c r="D53" s="55"/>
       <c r="E53" s="55"/>
@@ -24551,11 +24772,11 @@
         <v>2</v>
       </c>
       <c r="B54" s="53" t="s">
-        <v>91</v>
-      </c>
-      <c r="C54" s="54" t="n">
+        <v>97</v>
+      </c>
+      <c r="C54" s="54" t="str">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$8,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$8,Rekorde!$A$4:$A$17,0)),"")*0.7*2,0)/2)</f>
-        <v>45</v>
+        <v/>
       </c>
       <c r="D54" s="55"/>
       <c r="E54" s="55"/>
@@ -24568,11 +24789,11 @@
         <v>3</v>
       </c>
       <c r="B55" s="56" t="s">
-        <v>92</v>
-      </c>
-      <c r="C55" s="54" t="n">
+        <v>98</v>
+      </c>
+      <c r="C55" s="54" t="str">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$8,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$8,Rekorde!$A$4:$A$17,0)),"")*1*2,0)/2)</f>
-        <v>64.5</v>
+        <v/>
       </c>
       <c r="D55" s="55"/>
       <c r="E55" s="55"/>
@@ -24585,11 +24806,11 @@
         <v>4</v>
       </c>
       <c r="B56" s="56" t="s">
-        <v>92</v>
-      </c>
-      <c r="C56" s="54" t="n">
+        <v>98</v>
+      </c>
+      <c r="C56" s="54" t="str">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$8,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$8,Rekorde!$A$4:$A$17,0)),"")*1*2,0)/2)</f>
-        <v>64.5</v>
+        <v/>
       </c>
       <c r="D56" s="55"/>
       <c r="E56" s="55"/>
@@ -24601,10 +24822,13 @@
       <c r="A57" s="52" t="n">
         <v>5</v>
       </c>
-      <c r="B57" s="53" t="s">
-        <v>93</v>
-      </c>
-      <c r="C57" s="57"/>
+      <c r="B57" s="56" t="s">
+        <v>98</v>
+      </c>
+      <c r="C57" s="54" t="str">
+        <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$8,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$8,Rekorde!$A$4:$A$17,0)),"")*1*2,0)/2)</f>
+        <v/>
+      </c>
       <c r="D57" s="55"/>
       <c r="E57" s="55"/>
       <c r="F57" s="55"/>
@@ -24614,7 +24838,7 @@
     <row r="59" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="49" t="str">
         <f aca="false">Übungen!$A$9</f>
-        <v>Seitliche Kickbacks</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="B59" s="49"/>
       <c r="C59" s="49"/>
@@ -24626,8 +24850,8 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="50" t="str">
-        <f aca="false">IF(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$9,Rekorde!$A$4:$A$17,0)),"")="","noch keine Werte erfasst","Zuletzt: "&amp;TEXT(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$9,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg × "&amp;IF(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$9,Rekorde!$A$4:$A$17,0)),"")="","?",TEXT(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$9,Rekorde!$A$4:$A$17,0)),""),"0"))&amp;" Wdh     ·     Bestwert: "&amp;TEXT(IFERROR(INDEX(Rekorde!$F$4:$F$17,MATCH(Übungen!$A$9,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     Ziel heute: "&amp;TEXT(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$9,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     Ziel-Wdh: "&amp;Übungen!$D$9)</f>
-        <v>Zuletzt: 35 kg × 15 Wdh     ·     Bestwert: 49 kg     ·     Ziel heute: 36 kg     ·     Ziel-Wdh: 12-15</v>
+        <f aca="false">IF(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$9,Rekorde!$A$4:$A$17,0)),"")="",IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$9,Rekorde!$A$4:$A$17,0)),"")="","Neu im Plan - Startgewicht im Blatt 'Übungen' eintragen     ·     ","Neu im Plan     ·     Start: "&amp;TEXT(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$9,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     "),"Zuletzt: "&amp;TEXT(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$9,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg × "&amp;IF(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$9,Rekorde!$A$4:$A$17,0)),"")="","?",TEXT(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$9,Rekorde!$A$4:$A$17,0)),""),"0"))&amp;" Wdh     ·     Bestwert: "&amp;TEXT(IFERROR(INDEX(Rekorde!$F$4:$F$17,MATCH(Übungen!$A$9,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     "&amp;IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$9,Rekorde!$A$4:$A$17,0)),"")="","","Ziel heute: "&amp;TEXT(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$9,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     ")&amp;IF(AND(Übungen!$H$9&lt;&gt;"",IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$9,Rekorde!$A$4:$A$17,0)),"")&lt;&gt;"",IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$9,Rekorde!$A$4:$A$17,0)),"")&gt;=Übungen!$H$9),"Stackende, über Tempo und Pausen steigern     ·     ",""))&amp;"Vorgabe: "&amp;Übungen!$E$9&amp;" × "&amp;Übungen!$D$9&amp;" Wdh @ RPE "&amp;Übungen!$F$9</f>
+        <v>Zuletzt: 270 kg × 8 Wdh     ·     Bestwert: 280 kg     ·     Ziel heute: 277 kg     ·     Vorgabe: 3 × 8-12 Wdh @ RPE 8-9</v>
       </c>
       <c r="B60" s="50"/>
       <c r="C60" s="50"/>
@@ -24639,28 +24863,28 @@
     </row>
     <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="51" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B61" s="51" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C61" s="51" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="D61" s="51" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="E61" s="51" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F61" s="51" t="s">
         <v>39</v>
       </c>
       <c r="G61" s="51" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="H61" s="51" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24668,11 +24892,11 @@
         <v>1</v>
       </c>
       <c r="B62" s="53" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C62" s="54" t="n">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$9,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$9,Rekorde!$A$4:$A$17,0)),"")*0.45*2,0)/2)</f>
-        <v>16</v>
+        <v>124.5</v>
       </c>
       <c r="D62" s="55"/>
       <c r="E62" s="55"/>
@@ -24685,11 +24909,11 @@
         <v>2</v>
       </c>
       <c r="B63" s="53" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C63" s="54" t="n">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$9,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$9,Rekorde!$A$4:$A$17,0)),"")*0.7*2,0)/2)</f>
-        <v>25</v>
+        <v>194</v>
       </c>
       <c r="D63" s="55"/>
       <c r="E63" s="55"/>
@@ -24702,11 +24926,11 @@
         <v>3</v>
       </c>
       <c r="B64" s="56" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C64" s="54" t="n">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$9,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$9,Rekorde!$A$4:$A$17,0)),"")*1*2,0)/2)</f>
-        <v>36</v>
+        <v>277</v>
       </c>
       <c r="D64" s="55"/>
       <c r="E64" s="55"/>
@@ -24719,11 +24943,11 @@
         <v>4</v>
       </c>
       <c r="B65" s="56" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C65" s="54" t="n">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$9,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$9,Rekorde!$A$4:$A$17,0)),"")*1*2,0)/2)</f>
-        <v>36</v>
+        <v>277</v>
       </c>
       <c r="D65" s="55"/>
       <c r="E65" s="55"/>
@@ -24735,10 +24959,13 @@
       <c r="A66" s="52" t="n">
         <v>5</v>
       </c>
-      <c r="B66" s="53" t="s">
-        <v>93</v>
-      </c>
-      <c r="C66" s="57"/>
+      <c r="B66" s="56" t="s">
+        <v>98</v>
+      </c>
+      <c r="C66" s="54" t="n">
+        <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$9,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$9,Rekorde!$A$4:$A$17,0)),"")*1*2,0)/2)</f>
+        <v>277</v>
+      </c>
       <c r="D66" s="55"/>
       <c r="E66" s="55"/>
       <c r="F66" s="55"/>
@@ -24760,8 +24987,8 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="50" t="str">
-        <f aca="false">IF(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$10,Rekorde!$A$4:$A$17,0)),"")="","noch keine Werte erfasst","Zuletzt: "&amp;TEXT(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$10,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg × "&amp;IF(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$10,Rekorde!$A$4:$A$17,0)),"")="","?",TEXT(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$10,Rekorde!$A$4:$A$17,0)),""),"0"))&amp;" Wdh     ·     Bestwert: "&amp;TEXT(IFERROR(INDEX(Rekorde!$F$4:$F$17,MATCH(Übungen!$A$10,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     Ziel heute: "&amp;TEXT(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$10,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     Ziel-Wdh: "&amp;Übungen!$D$10)</f>
-        <v>Zuletzt: 45 kg × 15 Wdh     ·     Bestwert: 55 kg     ·     Ziel heute: 46 kg     ·     Ziel-Wdh: 10-15</v>
+        <f aca="false">IF(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$10,Rekorde!$A$4:$A$17,0)),"")="",IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$10,Rekorde!$A$4:$A$17,0)),"")="","Neu im Plan - Startgewicht im Blatt 'Übungen' eintragen     ·     ","Neu im Plan     ·     Start: "&amp;TEXT(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$10,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     "),"Zuletzt: "&amp;TEXT(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$10,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg × "&amp;IF(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$10,Rekorde!$A$4:$A$17,0)),"")="","?",TEXT(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$10,Rekorde!$A$4:$A$17,0)),""),"0"))&amp;" Wdh     ·     Bestwert: "&amp;TEXT(IFERROR(INDEX(Rekorde!$F$4:$F$17,MATCH(Übungen!$A$10,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     "&amp;IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$10,Rekorde!$A$4:$A$17,0)),"")="","","Ziel heute: "&amp;TEXT(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$10,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     ")&amp;IF(AND(Übungen!$H$10&lt;&gt;"",IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$10,Rekorde!$A$4:$A$17,0)),"")&lt;&gt;"",IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$10,Rekorde!$A$4:$A$17,0)),"")&gt;=Übungen!$H$10),"Stackende, über Tempo und Pausen steigern     ·     ",""))&amp;"Vorgabe: "&amp;Übungen!$E$10&amp;" × "&amp;Übungen!$D$10&amp;" Wdh @ RPE "&amp;Übungen!$F$10</f>
+        <v>Zuletzt: 45 kg × 15 Wdh     ·     Bestwert: 55 kg     ·     Ziel heute: 46 kg     ·     Vorgabe: 3 × 10-12 Wdh @ RPE 9</v>
       </c>
       <c r="B69" s="50"/>
       <c r="C69" s="50"/>
@@ -24773,28 +25000,28 @@
     </row>
     <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="51" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B70" s="51" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C70" s="51" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="D70" s="51" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="E70" s="51" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F70" s="51" t="s">
         <v>39</v>
       </c>
       <c r="G70" s="51" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="H70" s="51" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24802,7 +25029,7 @@
         <v>1</v>
       </c>
       <c r="B71" s="53" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C71" s="54" t="n">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$10,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$10,Rekorde!$A$4:$A$17,0)),"")*0.45*2,0)/2)</f>
@@ -24819,7 +25046,7 @@
         <v>2</v>
       </c>
       <c r="B72" s="53" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C72" s="54" t="n">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$10,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$10,Rekorde!$A$4:$A$17,0)),"")*0.7*2,0)/2)</f>
@@ -24836,7 +25063,7 @@
         <v>3</v>
       </c>
       <c r="B73" s="56" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C73" s="54" t="n">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$10,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$10,Rekorde!$A$4:$A$17,0)),"")*1*2,0)/2)</f>
@@ -24853,7 +25080,7 @@
         <v>4</v>
       </c>
       <c r="B74" s="56" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C74" s="54" t="n">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$10,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$10,Rekorde!$A$4:$A$17,0)),"")*1*2,0)/2)</f>
@@ -24870,7 +25097,7 @@
         <v>5</v>
       </c>
       <c r="B75" s="53" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C75" s="57"/>
       <c r="D75" s="55"/>
@@ -24882,7 +25109,7 @@
     <row r="77" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="49" t="str">
         <f aca="false">Übungen!$A$11</f>
-        <v>Hip Thrust</v>
+        <v>Seitliche Kickbacks</v>
       </c>
       <c r="B77" s="49"/>
       <c r="C77" s="49"/>
@@ -24894,8 +25121,8 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="50" t="str">
-        <f aca="false">IF(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$11,Rekorde!$A$4:$A$17,0)),"")="","noch keine Werte erfasst","Zuletzt: "&amp;TEXT(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$11,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg × "&amp;IF(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$11,Rekorde!$A$4:$A$17,0)),"")="","?",TEXT(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$11,Rekorde!$A$4:$A$17,0)),""),"0"))&amp;" Wdh     ·     Bestwert: "&amp;TEXT(IFERROR(INDEX(Rekorde!$F$4:$F$17,MATCH(Übungen!$A$11,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     Ziel heute: "&amp;TEXT(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$11,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     Ziel-Wdh: "&amp;Übungen!$D$11)</f>
-        <v>Zuletzt: 270 kg × 8 Wdh     ·     Bestwert: 280 kg     ·     Ziel heute: 277 kg     ·     Ziel-Wdh: 6-12</v>
+        <f aca="false">IF(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$11,Rekorde!$A$4:$A$17,0)),"")="",IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$11,Rekorde!$A$4:$A$17,0)),"")="","Neu im Plan - Startgewicht im Blatt 'Übungen' eintragen     ·     ","Neu im Plan     ·     Start: "&amp;TEXT(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$11,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     "),"Zuletzt: "&amp;TEXT(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$11,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg × "&amp;IF(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$11,Rekorde!$A$4:$A$17,0)),"")="","?",TEXT(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$11,Rekorde!$A$4:$A$17,0)),""),"0"))&amp;" Wdh     ·     Bestwert: "&amp;TEXT(IFERROR(INDEX(Rekorde!$F$4:$F$17,MATCH(Übungen!$A$11,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     "&amp;IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$11,Rekorde!$A$4:$A$17,0)),"")="","","Ziel heute: "&amp;TEXT(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$11,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     ")&amp;IF(AND(Übungen!$H$11&lt;&gt;"",IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$11,Rekorde!$A$4:$A$17,0)),"")&lt;&gt;"",IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$11,Rekorde!$A$4:$A$17,0)),"")&gt;=Übungen!$H$11),"Stackende, über Tempo und Pausen steigern     ·     ",""))&amp;"Vorgabe: "&amp;Übungen!$E$11&amp;" × "&amp;Übungen!$D$11&amp;" Wdh @ RPE "&amp;Übungen!$F$11</f>
+        <v>Zuletzt: 35 kg × 15 Wdh     ·     Bestwert: 49 kg     ·     Ziel heute: 36 kg     ·     Vorgabe: 3 × 15-20 Wdh @ RPE 9</v>
       </c>
       <c r="B78" s="50"/>
       <c r="C78" s="50"/>
@@ -24907,28 +25134,28 @@
     </row>
     <row r="79" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="51" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B79" s="51" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C79" s="51" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="D79" s="51" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="E79" s="51" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F79" s="51" t="s">
         <v>39</v>
       </c>
       <c r="G79" s="51" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="H79" s="51" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24936,11 +25163,11 @@
         <v>1</v>
       </c>
       <c r="B80" s="53" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C80" s="54" t="n">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$11,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$11,Rekorde!$A$4:$A$17,0)),"")*0.45*2,0)/2)</f>
-        <v>124.5</v>
+        <v>16</v>
       </c>
       <c r="D80" s="55"/>
       <c r="E80" s="55"/>
@@ -24953,11 +25180,11 @@
         <v>2</v>
       </c>
       <c r="B81" s="53" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C81" s="54" t="n">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$11,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$11,Rekorde!$A$4:$A$17,0)),"")*0.7*2,0)/2)</f>
-        <v>194</v>
+        <v>25</v>
       </c>
       <c r="D81" s="55"/>
       <c r="E81" s="55"/>
@@ -24970,11 +25197,11 @@
         <v>3</v>
       </c>
       <c r="B82" s="56" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C82" s="54" t="n">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$11,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$11,Rekorde!$A$4:$A$17,0)),"")*1*2,0)/2)</f>
-        <v>277</v>
+        <v>36</v>
       </c>
       <c r="D82" s="55"/>
       <c r="E82" s="55"/>
@@ -24987,11 +25214,11 @@
         <v>4</v>
       </c>
       <c r="B83" s="56" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C83" s="54" t="n">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$11,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$11,Rekorde!$A$4:$A$17,0)),"")*1*2,0)/2)</f>
-        <v>277</v>
+        <v>36</v>
       </c>
       <c r="D83" s="55"/>
       <c r="E83" s="55"/>
@@ -25003,10 +25230,13 @@
       <c r="A84" s="52" t="n">
         <v>5</v>
       </c>
-      <c r="B84" s="53" t="s">
-        <v>93</v>
-      </c>
-      <c r="C84" s="57"/>
+      <c r="B84" s="56" t="s">
+        <v>98</v>
+      </c>
+      <c r="C84" s="54" t="n">
+        <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$11,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$11,Rekorde!$A$4:$A$17,0)),"")*1*2,0)/2)</f>
+        <v>36</v>
+      </c>
       <c r="D84" s="55"/>
       <c r="E84" s="55"/>
       <c r="F84" s="55"/>
@@ -25028,8 +25258,8 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="50" t="str">
-        <f aca="false">IF(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$12,Rekorde!$A$4:$A$17,0)),"")="","noch keine Werte erfasst","Zuletzt: "&amp;TEXT(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$12,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg × "&amp;IF(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$12,Rekorde!$A$4:$A$17,0)),"")="","?",TEXT(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$12,Rekorde!$A$4:$A$17,0)),""),"0"))&amp;" Wdh     ·     Bestwert: "&amp;TEXT(IFERROR(INDEX(Rekorde!$F$4:$F$17,MATCH(Übungen!$A$12,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     Ziel heute: "&amp;TEXT(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$12,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     Ziel-Wdh: "&amp;Übungen!$D$12)</f>
-        <v>Zuletzt: 150 kg × 12 Wdh     ·     Bestwert: 150 kg     ·     Ziel heute: 154 kg     ·     Ziel-Wdh: 12-15</v>
+        <f aca="false">IF(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$12,Rekorde!$A$4:$A$17,0)),"")="",IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$12,Rekorde!$A$4:$A$17,0)),"")="","Neu im Plan - Startgewicht im Blatt 'Übungen' eintragen     ·     ","Neu im Plan     ·     Start: "&amp;TEXT(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$12,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     "),"Zuletzt: "&amp;TEXT(IFERROR(INDEX(Rekorde!$L$4:$L$17,MATCH(Übungen!$A$12,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg × "&amp;IF(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$12,Rekorde!$A$4:$A$17,0)),"")="","?",TEXT(IFERROR(INDEX(Rekorde!$M$4:$M$17,MATCH(Übungen!$A$12,Rekorde!$A$4:$A$17,0)),""),"0"))&amp;" Wdh     ·     Bestwert: "&amp;TEXT(IFERROR(INDEX(Rekorde!$F$4:$F$17,MATCH(Übungen!$A$12,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     "&amp;IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$12,Rekorde!$A$4:$A$17,0)),"")="","","Ziel heute: "&amp;TEXT(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$12,Rekorde!$A$4:$A$17,0)),""),"0.#")&amp;" kg     ·     ")&amp;IF(AND(Übungen!$H$12&lt;&gt;"",IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$12,Rekorde!$A$4:$A$17,0)),"")&lt;&gt;"",IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$12,Rekorde!$A$4:$A$17,0)),"")&gt;=Übungen!$H$12),"Stackende, über Tempo und Pausen steigern     ·     ",""))&amp;"Vorgabe: "&amp;Übungen!$E$12&amp;" × "&amp;Übungen!$D$12&amp;" Wdh @ RPE "&amp;Übungen!$F$12</f>
+        <v>Zuletzt: 150 kg × 12 Wdh     ·     Bestwert: 150 kg     ·     Ziel heute: 154 kg     ·     Vorgabe: 3 × 10-15 Wdh @ RPE 9</v>
       </c>
       <c r="B87" s="50"/>
       <c r="C87" s="50"/>
@@ -25041,28 +25271,28 @@
     </row>
     <row r="88" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="51" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B88" s="51" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C88" s="51" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="D88" s="51" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="E88" s="51" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F88" s="51" t="s">
         <v>39</v>
       </c>
       <c r="G88" s="51" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="H88" s="51" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25070,7 +25300,7 @@
         <v>1</v>
       </c>
       <c r="B89" s="53" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C89" s="54" t="n">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$12,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$12,Rekorde!$A$4:$A$17,0)),"")*0.45*2,0)/2)</f>
@@ -25087,7 +25317,7 @@
         <v>2</v>
       </c>
       <c r="B90" s="53" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C90" s="54" t="n">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$12,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$12,Rekorde!$A$4:$A$17,0)),"")*0.7*2,0)/2)</f>
@@ -25104,7 +25334,7 @@
         <v>3</v>
       </c>
       <c r="B91" s="56" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C91" s="54" t="n">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$12,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$12,Rekorde!$A$4:$A$17,0)),"")*1*2,0)/2)</f>
@@ -25121,7 +25351,7 @@
         <v>4</v>
       </c>
       <c r="B92" s="56" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C92" s="54" t="n">
         <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$12,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$12,Rekorde!$A$4:$A$17,0)),"")*1*2,0)/2)</f>
@@ -25137,10 +25367,13 @@
       <c r="A93" s="52" t="n">
         <v>5</v>
       </c>
-      <c r="B93" s="53" t="s">
-        <v>93</v>
-      </c>
-      <c r="C93" s="57"/>
+      <c r="B93" s="56" t="s">
+        <v>98</v>
+      </c>
+      <c r="C93" s="54" t="n">
+        <f aca="false">IF(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$12,Rekorde!$A$4:$A$17,0)),"")="","",ROUND(IFERROR(INDEX(Rekorde!$N$4:$N$17,MATCH(Übungen!$A$12,Rekorde!$A$4:$A$17,0)),"")*1*2,0)/2)</f>
+        <v>154</v>
+      </c>
       <c r="D93" s="55"/>
       <c r="E93" s="55"/>
       <c r="F93" s="55"/>
@@ -25149,7 +25382,7 @@
     </row>
     <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="3" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -25237,7 +25470,7 @@
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;L&amp;8 &amp;K808080Gym Logbuch  |  Beintraining&amp;R&amp;8 &amp;K808080Trainingsblatt</oddHeader>
-    <oddFooter>&amp;L&amp;8 &amp;K808080Plan (kg) = Aufwärm-Rampe 45 % / 70 % auf das Ziel aus dem Blatt 'Rekorde'&amp;R&amp;8 &amp;K808080Seite &amp;P von &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;8 &amp;K808080Plan (kg) = Aufwärm-Rampe 45 % / 70 %, dann Zielgewicht aus dem Blatt 'Rekorde'&amp;R&amp;8 &amp;K808080Seite &amp;P von &amp;N</oddFooter>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="44" man="true" max="16383" min="0"/>
@@ -25250,234 +25483,380 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="J3" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="B3" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="F4" s="19"/>
-    </row>
-    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>179</v>
+      </c>
+      <c r="E4" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>180</v>
+      </c>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="J4" s="59" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>170</v>
-      </c>
-      <c r="E5" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="F5" s="19"/>
-    </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>184</v>
+      </c>
+      <c r="E5" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="J5" s="59" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>172</v>
-      </c>
-      <c r="E6" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="F6" s="19"/>
-    </row>
-    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>188</v>
+      </c>
+      <c r="E6" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="J6" s="59" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="E7" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="F7" s="19"/>
-    </row>
-    <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>191</v>
+      </c>
+      <c r="E7" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="I7" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="J7" s="59" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>108</v>
+        <v>193</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="D8" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="E8" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="J8" s="59" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="E9" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="27" t="s">
+        <v>180</v>
+      </c>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="J9" s="59" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="E10" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="J10" s="59" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="E11" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="J11" s="59" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="E12" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="J12" s="59" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="60" t="s">
         <v>177</v>
       </c>
-      <c r="E8" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="F8" s="19"/>
-    </row>
-    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="E9" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="F9" s="19"/>
-    </row>
-    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="F10" s="19"/>
-    </row>
-    <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="C13" s="60" t="s">
+        <v>206</v>
+      </c>
+      <c r="D13" s="61" t="s">
+        <v>200</v>
+      </c>
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="62"/>
+      <c r="H13" s="62"/>
+      <c r="I13" s="61" t="s">
+        <v>207</v>
+      </c>
+      <c r="J13" s="63" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="60" t="s">
         <v>114</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="D11" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="E11" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="F11" s="19"/>
-    </row>
-    <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="D12" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="F12" s="19"/>
-    </row>
-    <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="19"/>
-    </row>
-    <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="19"/>
+      <c r="B14" s="60" t="s">
+        <v>194</v>
+      </c>
+      <c r="C14" s="60" t="s">
+        <v>209</v>
+      </c>
+      <c r="D14" s="61" t="s">
+        <v>204</v>
+      </c>
+      <c r="E14" s="61"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="61" t="s">
+        <v>207</v>
+      </c>
+      <c r="J14" s="63" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="19"/>
@@ -25485,7 +25864,11 @@
       <c r="C15" s="19"/>
       <c r="D15" s="27"/>
       <c r="E15" s="27"/>
-      <c r="F15" s="19"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="59"/>
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="19"/>
@@ -25493,7 +25876,11 @@
       <c r="C16" s="19"/>
       <c r="D16" s="27"/>
       <c r="E16" s="27"/>
-      <c r="F16" s="19"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="59"/>
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="19"/>
@@ -25501,27 +25888,45 @@
       <c r="C17" s="19"/>
       <c r="D17" s="27"/>
       <c r="E17" s="27"/>
-      <c r="F17" s="19"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="15" t="s">
-        <v>182</v>
-      </c>
+      <c r="F17" s="27"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="59"/>
+    </row>
+    <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="42" t="s">
+        <v>211</v>
+      </c>
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="42"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A19:J19"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B4:B17" type="list">
       <formula1>"Beine vorne,Beine hinten"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="ja = Teil der Planung, nein = Archiv. Die Historie bleibt in beiden Fällen erhalten." errorStyle="stop" errorTitle="Aktiv" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I4:I17" type="list">
+      <formula1>"ja,nein"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.5" right="0.4" top="0.7" bottom="0.6" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;L&amp;8 &amp;K808080Gym Logbuch  |  Beintraining&amp;R&amp;8 &amp;K808080Übungen</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K808080Quelle: Löwin_Training_260727.pdf&amp;R&amp;8 &amp;K808080Seite &amp;P von &amp;N</oddFooter>
